--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
@@ -137,9 +137,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_USA_Major_" displayName="AveragesTable_USA_Major_" ref="A1:DD31" headerRowCount="1">
-  <autoFilter ref="A1:DD31"/>
-  <tableColumns count="108">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_USA_Major_" displayName="AveragesTable_USA_Major_" ref="A1:EC31" headerRowCount="1">
+  <autoFilter ref="A1:EC31"/>
+  <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>
     <tableColumn id="2" name="total_games"/>
     <tableColumn id="3" name="home_games"/>
@@ -248,6 +248,31 @@
     <tableColumn id="106" name="avg_pinnacle_ft_over15_odd"/>
     <tableColumn id="107" name="avg_pinnacle_ft_over25_odd"/>
     <tableColumn id="108" name="avg_pinnacle_ft_over35_odd"/>
+    <tableColumn id="109" name="total_avg_0_10_min_goals"/>
+    <tableColumn id="110" name="total_avg_2h_cards"/>
+    <tableColumn id="111" name="total_avg_2h_corners"/>
+    <tableColumn id="112" name="total_avg_attacks"/>
+    <tableColumn id="113" name="total_avg_cards_0_10_min"/>
+    <tableColumn id="114" name="total_avg_cards_num"/>
+    <tableColumn id="115" name="total_avg_corners"/>
+    <tableColumn id="116" name="total_avg_corners_0_10_min"/>
+    <tableColumn id="117" name="total_avg_dangerous_attacks"/>
+    <tableColumn id="118" name="total_avg_fh_cards"/>
+    <tableColumn id="119" name="total_avg_fh_corners"/>
+    <tableColumn id="120" name="total_avg_fouls"/>
+    <tableColumn id="121" name="total_avg_freekicks"/>
+    <tableColumn id="122" name="total_avg_goalkicks"/>
+    <tableColumn id="123" name="total_avg_penalties_won"/>
+    <tableColumn id="124" name="total_avg_penalty_goals"/>
+    <tableColumn id="125" name="total_avg_penalty_missed"/>
+    <tableColumn id="126" name="total_avg_possession"/>
+    <tableColumn id="127" name="total_avg_red_cards"/>
+    <tableColumn id="128" name="total_avg_shots"/>
+    <tableColumn id="129" name="total_avg_shotsOffTarget"/>
+    <tableColumn id="130" name="total_avg_shotsOnTarget"/>
+    <tableColumn id="131" name="total_avg_throwins"/>
+    <tableColumn id="132" name="total_avg_xg"/>
+    <tableColumn id="133" name="total_avg_yellow_cards"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -542,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD31"/>
+  <dimension ref="A1:EC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.8" customWidth="1" min="1" max="1"/>
@@ -653,6 +678,31 @@
     <col width="33.6" customWidth="1" min="106" max="106"/>
     <col width="33.6" customWidth="1" min="107" max="107"/>
     <col width="33.6" customWidth="1" min="108" max="108"/>
+    <col width="31.2" customWidth="1" min="109" max="109"/>
+    <col width="24" customWidth="1" min="110" max="110"/>
+    <col width="26.4" customWidth="1" min="111" max="111"/>
+    <col width="22.8" customWidth="1" min="112" max="112"/>
+    <col width="31.2" customWidth="1" min="113" max="113"/>
+    <col width="25.2" customWidth="1" min="114" max="114"/>
+    <col width="22.8" customWidth="1" min="115" max="115"/>
+    <col width="33.6" customWidth="1" min="116" max="116"/>
+    <col width="34.8" customWidth="1" min="117" max="117"/>
+    <col width="24" customWidth="1" min="118" max="118"/>
+    <col width="26.4" customWidth="1" min="119" max="119"/>
+    <col width="20.4" customWidth="1" min="120" max="120"/>
+    <col width="25.2" customWidth="1" min="121" max="121"/>
+    <col width="25.2" customWidth="1" min="122" max="122"/>
+    <col width="30" customWidth="1" min="123" max="123"/>
+    <col width="30" customWidth="1" min="124" max="124"/>
+    <col width="31.2" customWidth="1" min="125" max="125"/>
+    <col width="26.4" customWidth="1" min="126" max="126"/>
+    <col width="25.2" customWidth="1" min="127" max="127"/>
+    <col width="20.4" customWidth="1" min="128" max="128"/>
+    <col width="31.2" customWidth="1" min="129" max="129"/>
+    <col width="30" customWidth="1" min="130" max="130"/>
+    <col width="24" customWidth="1" min="131" max="131"/>
+    <col width="16.8" customWidth="1" min="132" max="132"/>
+    <col width="28.8" customWidth="1" min="133" max="133"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1196,6 +1246,131 @@
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_0_10_min_goals</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_2h_cards</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_2h_corners</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_attacks</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_cards_0_10_min</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_cards_num</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_corners</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_corners_0_10_min</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_fh_cards</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_fh_corners</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_fouls</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_freekicks</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_goalkicks</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_penalties_won</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_penalty_goals</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_penalty_missed</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_possession</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_red_cards</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_shots</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_shotsOffTarget</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_shotsOnTarget</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_throwins</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_xg</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_yellow_cards</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1204,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -1243,43 +1418,43 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
         <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>26</v>
+        <v>28.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AT2" t="n">
         <v>2</v>
@@ -1297,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1306,52 +1481,52 @@
         <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="BF2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BG2" t="n">
         <v>2</v>
       </c>
       <c r="BH2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BI2" t="n">
         <v>2</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
@@ -1377,81 +1552,81 @@
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="inlineStr"/>
       <c r="CA2" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="CB2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="CC2" t="n">
         <v>3.64</v>
       </c>
-      <c r="CC2" t="n">
-        <v>3.91</v>
-      </c>
       <c r="CD2" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="CM2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CQ2" t="n">
         <v>2.4</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>2.48</v>
       </c>
       <c r="CR2" t="inlineStr"/>
       <c r="CS2" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CT2" t="inlineStr"/>
       <c r="CU2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX2" t="n">
         <v>1.52</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.41</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="DB2" t="n">
         <v>1.24</v>
@@ -1462,6 +1637,31 @@
       <c r="DD2" t="n">
         <v>2.84</v>
       </c>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="inlineStr"/>
+      <c r="DK2" t="inlineStr"/>
+      <c r="DL2" t="inlineStr"/>
+      <c r="DM2" t="inlineStr"/>
+      <c r="DN2" t="inlineStr"/>
+      <c r="DO2" t="inlineStr"/>
+      <c r="DP2" t="inlineStr"/>
+      <c r="DQ2" t="inlineStr"/>
+      <c r="DR2" t="inlineStr"/>
+      <c r="DS2" t="inlineStr"/>
+      <c r="DT2" t="inlineStr"/>
+      <c r="DU2" t="inlineStr"/>
+      <c r="DV2" t="inlineStr"/>
+      <c r="DW2" t="inlineStr"/>
+      <c r="DX2" t="inlineStr"/>
+      <c r="DY2" t="inlineStr"/>
+      <c r="DZ2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1732,6 +1932,31 @@
       <c r="DD3" t="n">
         <v>3.31</v>
       </c>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="inlineStr"/>
+      <c r="DI3" t="inlineStr"/>
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="inlineStr"/>
+      <c r="DL3" t="inlineStr"/>
+      <c r="DM3" t="inlineStr"/>
+      <c r="DN3" t="inlineStr"/>
+      <c r="DO3" t="inlineStr"/>
+      <c r="DP3" t="inlineStr"/>
+      <c r="DQ3" t="inlineStr"/>
+      <c r="DR3" t="inlineStr"/>
+      <c r="DS3" t="inlineStr"/>
+      <c r="DT3" t="inlineStr"/>
+      <c r="DU3" t="inlineStr"/>
+      <c r="DV3" t="inlineStr"/>
+      <c r="DW3" t="inlineStr"/>
+      <c r="DX3" t="inlineStr"/>
+      <c r="DY3" t="inlineStr"/>
+      <c r="DZ3" t="inlineStr"/>
+      <c r="EA3" t="inlineStr"/>
+      <c r="EB3" t="inlineStr"/>
+      <c r="EC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1740,13 +1965,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -1779,115 +2004,115 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>105</v>
+        <v>96.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH4" t="n">
         <v>8</v>
       </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>7</v>
-      </c>
       <c r="BI4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BM4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -1896,7 +2121,7 @@
         <v>100</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
         <v>0</v>
@@ -1908,21 +2133,21 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="inlineStr"/>
       <c r="CA4" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.72</v>
+        <v>3.17</v>
       </c>
       <c r="CE4" t="n">
         <v>1.28</v>
@@ -1937,25 +2162,25 @@
         <v>1.56</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CK4" t="n">
         <v>1.38</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP4" t="n">
         <v>1.65</v>
@@ -1968,18 +2193,18 @@
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="inlineStr"/>
       <c r="CV4" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CX4" t="inlineStr"/>
       <c r="CY4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CZ4" t="inlineStr"/>
       <c r="DA4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB4" t="n">
         <v>1.21</v>
@@ -1990,6 +2215,31 @@
       <c r="DD4" t="n">
         <v>2.66</v>
       </c>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="inlineStr"/>
+      <c r="DJ4" t="inlineStr"/>
+      <c r="DK4" t="inlineStr"/>
+      <c r="DL4" t="inlineStr"/>
+      <c r="DM4" t="inlineStr"/>
+      <c r="DN4" t="inlineStr"/>
+      <c r="DO4" t="inlineStr"/>
+      <c r="DP4" t="inlineStr"/>
+      <c r="DQ4" t="inlineStr"/>
+      <c r="DR4" t="inlineStr"/>
+      <c r="DS4" t="inlineStr"/>
+      <c r="DT4" t="inlineStr"/>
+      <c r="DU4" t="inlineStr"/>
+      <c r="DV4" t="inlineStr"/>
+      <c r="DW4" t="inlineStr"/>
+      <c r="DX4" t="inlineStr"/>
+      <c r="DY4" t="inlineStr"/>
+      <c r="DZ4" t="inlineStr"/>
+      <c r="EA4" t="inlineStr"/>
+      <c r="EB4" t="inlineStr"/>
+      <c r="EC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1998,41 +2248,95 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>67</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>33</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
@@ -2118,16 +2422,16 @@
         <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BI5" t="n">
         <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
         <v>2</v>
@@ -2142,10 +2446,10 @@
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
@@ -2166,15 +2470,19 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>100</v>
-      </c>
-      <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1.56</v>
+      </c>
       <c r="CA5" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.64</v>
+        <v>4.08</v>
       </c>
       <c r="CC5" t="n">
         <v>2.8</v>
@@ -2183,74 +2491,153 @@
         <v>3.01</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CR5" t="inlineStr"/>
+      <c r="CS5" t="n">
         <v>2.4</v>
       </c>
-      <c r="CG5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="CH5" t="n">
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CX5" t="n">
         <v>1.5</v>
       </c>
-      <c r="CI5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CR5" t="inlineStr"/>
-      <c r="CS5" t="inlineStr"/>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="inlineStr"/>
-      <c r="CV5" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>1.46</v>
-      </c>
       <c r="CY5" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="DA5" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>16</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
@@ -2260,41 +2647,95 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>70</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>41</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>15</v>
+      </c>
+      <c r="R6" t="n">
+        <v>11</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
@@ -2380,7 +2821,7 @@
         <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BI6" t="n">
         <v>2</v>
@@ -2430,13 +2871,17 @@
       <c r="BX6" t="n">
         <v>0</v>
       </c>
-      <c r="BY6" t="inlineStr"/>
-      <c r="BZ6" t="inlineStr"/>
+      <c r="BY6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>2.14</v>
+      </c>
       <c r="CA6" t="n">
-        <v>4.65</v>
+        <v>4.25</v>
       </c>
       <c r="CB6" t="n">
-        <v>5.53</v>
+        <v>4.69</v>
       </c>
       <c r="CC6" t="n">
         <v>6.6</v>
@@ -2445,43 +2890,43 @@
         <v>8.16</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="CH6" t="n">
         <v>1.6</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.07</v>
+        <v>2.34</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="CO6" t="n">
         <v>1.17</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CR6" t="inlineStr"/>
       <c r="CS6" t="n">
@@ -2492,27 +2937,102 @@
         <v>1.72</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.14</v>
+        <v>2.39</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CZ6" t="inlineStr"/>
       <c r="DA6" t="n">
         <v>2.11</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>74</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>8</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>8</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2522,13 +3042,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -2558,118 +3078,118 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AG7" t="n">
         <v>1</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>56</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB7" t="n">
         <v>8</v>
       </c>
-      <c r="AM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>54</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB7" t="n">
+      <c r="BC7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH7" t="n">
         <v>11</v>
       </c>
-      <c r="BC7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>14</v>
-      </c>
       <c r="BI7" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
@@ -2684,7 +3204,7 @@
         <v>100</v>
       </c>
       <c r="BV7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
@@ -2695,55 +3215,55 @@
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="inlineStr"/>
       <c r="CA7" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.69</v>
+        <v>4.08</v>
       </c>
       <c r="CC7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CQ7" t="n">
         <v>2.3</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>2.4</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
@@ -2754,26 +3274,57 @@
         <v>1.62</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CW7" t="n">
         <v>1.48</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="DB7" t="inlineStr"/>
-      <c r="DC7" t="inlineStr"/>
-      <c r="DD7" t="inlineStr"/>
+        <v>1.83</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="inlineStr"/>
+      <c r="DG7" t="inlineStr"/>
+      <c r="DH7" t="inlineStr"/>
+      <c r="DI7" t="inlineStr"/>
+      <c r="DJ7" t="inlineStr"/>
+      <c r="DK7" t="inlineStr"/>
+      <c r="DL7" t="inlineStr"/>
+      <c r="DM7" t="inlineStr"/>
+      <c r="DN7" t="inlineStr"/>
+      <c r="DO7" t="inlineStr"/>
+      <c r="DP7" t="inlineStr"/>
+      <c r="DQ7" t="inlineStr"/>
+      <c r="DR7" t="inlineStr"/>
+      <c r="DS7" t="inlineStr"/>
+      <c r="DT7" t="inlineStr"/>
+      <c r="DU7" t="inlineStr"/>
+      <c r="DV7" t="inlineStr"/>
+      <c r="DW7" t="inlineStr"/>
+      <c r="DX7" t="inlineStr"/>
+      <c r="DY7" t="inlineStr"/>
+      <c r="DZ7" t="inlineStr"/>
+      <c r="EA7" t="inlineStr"/>
+      <c r="EB7" t="inlineStr"/>
+      <c r="EC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3044,6 +3595,31 @@
       <c r="DD8" t="n">
         <v>4</v>
       </c>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="inlineStr"/>
+      <c r="DG8" t="inlineStr"/>
+      <c r="DH8" t="inlineStr"/>
+      <c r="DI8" t="inlineStr"/>
+      <c r="DJ8" t="inlineStr"/>
+      <c r="DK8" t="inlineStr"/>
+      <c r="DL8" t="inlineStr"/>
+      <c r="DM8" t="inlineStr"/>
+      <c r="DN8" t="inlineStr"/>
+      <c r="DO8" t="inlineStr"/>
+      <c r="DP8" t="inlineStr"/>
+      <c r="DQ8" t="inlineStr"/>
+      <c r="DR8" t="inlineStr"/>
+      <c r="DS8" t="inlineStr"/>
+      <c r="DT8" t="inlineStr"/>
+      <c r="DU8" t="inlineStr"/>
+      <c r="DV8" t="inlineStr"/>
+      <c r="DW8" t="inlineStr"/>
+      <c r="DX8" t="inlineStr"/>
+      <c r="DY8" t="inlineStr"/>
+      <c r="DZ8" t="inlineStr"/>
+      <c r="EA8" t="inlineStr"/>
+      <c r="EB8" t="inlineStr"/>
+      <c r="EC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3052,13 +3628,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -3141,41 +3717,95 @@
       <c r="AE9" t="n">
         <v>1</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>127</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>63</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
       <c r="BG9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BI9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BJ9" t="n">
         <v>0</v>
@@ -3184,28 +3814,28 @@
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BM9" t="n">
         <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BO9" t="n">
         <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BT9" t="n">
         <v>0</v>
@@ -3229,51 +3859,55 @@
         <v>2</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="CC9" t="inlineStr"/>
-      <c r="CD9" t="inlineStr"/>
+        <v>3.55</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>3.17</v>
+      </c>
       <c r="CE9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM9" t="n">
         <v>2.4</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP9" t="n">
         <v>1.65</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="CR9" t="inlineStr"/>
       <c r="CS9" t="n">
@@ -3284,10 +3918,10 @@
         <v>1.51</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX9" t="n">
         <v>1.52</v>
@@ -3302,13 +3936,88 @@
         <v>1.91</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>8</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>12</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>17</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
@@ -3318,61 +4027,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -3384,28 +4093,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AA10" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
@@ -3435,111 +4144,111 @@
       <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BI10" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="BJ10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO10" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="BP10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BR10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BS10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BT10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.01</v>
+        <v>2.34</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.66</v>
+        <v>3.59</v>
       </c>
       <c r="CC10" t="inlineStr"/>
       <c r="CD10" t="inlineStr"/>
       <c r="CE10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
@@ -3554,32 +4263,57 @@
         <v>1.5</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.89</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="inlineStr"/>
+      <c r="DG10" t="inlineStr"/>
+      <c r="DH10" t="inlineStr"/>
+      <c r="DI10" t="inlineStr"/>
+      <c r="DJ10" t="inlineStr"/>
+      <c r="DK10" t="inlineStr"/>
+      <c r="DL10" t="inlineStr"/>
+      <c r="DM10" t="inlineStr"/>
+      <c r="DN10" t="inlineStr"/>
+      <c r="DO10" t="inlineStr"/>
+      <c r="DP10" t="inlineStr"/>
+      <c r="DQ10" t="inlineStr"/>
+      <c r="DR10" t="inlineStr"/>
+      <c r="DS10" t="inlineStr"/>
+      <c r="DT10" t="inlineStr"/>
+      <c r="DU10" t="inlineStr"/>
+      <c r="DV10" t="inlineStr"/>
+      <c r="DW10" t="inlineStr"/>
+      <c r="DX10" t="inlineStr"/>
+      <c r="DY10" t="inlineStr"/>
+      <c r="DZ10" t="inlineStr"/>
+      <c r="EA10" t="inlineStr"/>
+      <c r="EB10" t="inlineStr"/>
+      <c r="EC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3588,10 +4322,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -3600,82 +4334,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>17</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
         <v>11</v>
       </c>
-      <c r="Q11" t="n">
-        <v>20</v>
-      </c>
-      <c r="R11" t="n">
-        <v>4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>43</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>10</v>
-      </c>
       <c r="AA11" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
@@ -3705,37 +4439,37 @@
       <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
         <v>0</v>
       </c>
       <c r="BK11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN11" t="n">
         <v>2</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
@@ -3744,7 +4478,7 @@
         <v>100</v>
       </c>
       <c r="BT11" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
@@ -3756,92 +4490,125 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.32</v>
+        <v>3.04</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.64</v>
+        <v>3.76</v>
       </c>
       <c r="CC11" t="inlineStr"/>
       <c r="CD11" t="inlineStr"/>
       <c r="CE11" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CK11" t="n">
         <v>1.44</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="CN11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CR11" t="inlineStr"/>
-      <c r="CS11" t="inlineStr"/>
-      <c r="CT11" t="inlineStr"/>
-      <c r="CU11" t="inlineStr"/>
+        <v>2.81</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>1.54</v>
+      </c>
       <c r="CV11" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="DA11" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.64</v>
-      </c>
+        <v>2.72</v>
+      </c>
+      <c r="DE11" t="inlineStr"/>
+      <c r="DF11" t="inlineStr"/>
+      <c r="DG11" t="inlineStr"/>
+      <c r="DH11" t="inlineStr"/>
+      <c r="DI11" t="inlineStr"/>
+      <c r="DJ11" t="inlineStr"/>
+      <c r="DK11" t="inlineStr"/>
+      <c r="DL11" t="inlineStr"/>
+      <c r="DM11" t="inlineStr"/>
+      <c r="DN11" t="inlineStr"/>
+      <c r="DO11" t="inlineStr"/>
+      <c r="DP11" t="inlineStr"/>
+      <c r="DQ11" t="inlineStr"/>
+      <c r="DR11" t="inlineStr"/>
+      <c r="DS11" t="inlineStr"/>
+      <c r="DT11" t="inlineStr"/>
+      <c r="DU11" t="inlineStr"/>
+      <c r="DV11" t="inlineStr"/>
+      <c r="DW11" t="inlineStr"/>
+      <c r="DX11" t="inlineStr"/>
+      <c r="DY11" t="inlineStr"/>
+      <c r="DZ11" t="inlineStr"/>
+      <c r="EA11" t="inlineStr"/>
+      <c r="EB11" t="inlineStr"/>
+      <c r="EC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4108,6 +4875,31 @@
       <c r="DD12" t="n">
         <v>2.18</v>
       </c>
+      <c r="DE12" t="inlineStr"/>
+      <c r="DF12" t="inlineStr"/>
+      <c r="DG12" t="inlineStr"/>
+      <c r="DH12" t="inlineStr"/>
+      <c r="DI12" t="inlineStr"/>
+      <c r="DJ12" t="inlineStr"/>
+      <c r="DK12" t="inlineStr"/>
+      <c r="DL12" t="inlineStr"/>
+      <c r="DM12" t="inlineStr"/>
+      <c r="DN12" t="inlineStr"/>
+      <c r="DO12" t="inlineStr"/>
+      <c r="DP12" t="inlineStr"/>
+      <c r="DQ12" t="inlineStr"/>
+      <c r="DR12" t="inlineStr"/>
+      <c r="DS12" t="inlineStr"/>
+      <c r="DT12" t="inlineStr"/>
+      <c r="DU12" t="inlineStr"/>
+      <c r="DV12" t="inlineStr"/>
+      <c r="DW12" t="inlineStr"/>
+      <c r="DX12" t="inlineStr"/>
+      <c r="DY12" t="inlineStr"/>
+      <c r="DZ12" t="inlineStr"/>
+      <c r="EA12" t="inlineStr"/>
+      <c r="EB12" t="inlineStr"/>
+      <c r="EC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4116,10 +4908,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -4131,76 +4923,76 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
+        <v>9</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z13" t="n">
         <v>11</v>
       </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>36</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>8</v>
-      </c>
       <c r="AA13" t="n">
         <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC13" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -4233,16 +5025,16 @@
       <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
       <c r="BG13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BI13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
@@ -4251,19 +5043,19 @@
         <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP13" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -4272,7 +5064,7 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
         <v>0</v>
@@ -4284,39 +5076,39 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="CC13" t="inlineStr"/>
       <c r="CD13" t="inlineStr"/>
       <c r="CE13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CK13" t="n">
         <v>1.38</v>
@@ -4325,19 +5117,19 @@
         <v>1.71</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO13" t="n">
         <v>1.18</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CR13" t="n">
         <v>1.34</v>
@@ -4352,32 +5144,57 @@
         <v>1.51</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CX13" t="n">
         <v>1.61</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.22</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.86</v>
-      </c>
+        <v>2.76</v>
+      </c>
+      <c r="DE13" t="inlineStr"/>
+      <c r="DF13" t="inlineStr"/>
+      <c r="DG13" t="inlineStr"/>
+      <c r="DH13" t="inlineStr"/>
+      <c r="DI13" t="inlineStr"/>
+      <c r="DJ13" t="inlineStr"/>
+      <c r="DK13" t="inlineStr"/>
+      <c r="DL13" t="inlineStr"/>
+      <c r="DM13" t="inlineStr"/>
+      <c r="DN13" t="inlineStr"/>
+      <c r="DO13" t="inlineStr"/>
+      <c r="DP13" t="inlineStr"/>
+      <c r="DQ13" t="inlineStr"/>
+      <c r="DR13" t="inlineStr"/>
+      <c r="DS13" t="inlineStr"/>
+      <c r="DT13" t="inlineStr"/>
+      <c r="DU13" t="inlineStr"/>
+      <c r="DV13" t="inlineStr"/>
+      <c r="DW13" t="inlineStr"/>
+      <c r="DX13" t="inlineStr"/>
+      <c r="DY13" t="inlineStr"/>
+      <c r="DZ13" t="inlineStr"/>
+      <c r="EA13" t="inlineStr"/>
+      <c r="EB13" t="inlineStr"/>
+      <c r="EC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4386,13 +5203,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4475,65 +5292,119 @@
       <c r="AE14" t="n">
         <v>1</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>137</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>71</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3</v>
+      </c>
       <c r="BG14" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN14" t="n">
         <v>2</v>
       </c>
       <c r="BO14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BP14" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
@@ -4542,7 +5413,7 @@
         <v>100</v>
       </c>
       <c r="BT14" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
         <v>0</v>
@@ -4563,86 +5434,169 @@
         <v>1.93</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="CC14" t="inlineStr"/>
-      <c r="CD14" t="inlineStr"/>
+        <v>3.99</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>1.95</v>
+      </c>
       <c r="CE14" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="CH14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CU14" t="n">
         <v>1.62</v>
       </c>
-      <c r="CI14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="CJ14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CN14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CO14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CP14" t="n">
+      <c r="CV14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
         <v>1.5</v>
       </c>
-      <c r="CQ14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CR14" t="inlineStr"/>
-      <c r="CS14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="CT14" t="inlineStr"/>
-      <c r="CU14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CV14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CW14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CX14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>2.18</v>
+      <c r="DG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>6</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>62</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>13</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>11</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>4</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>6</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>13</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -4652,41 +5606,95 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>88</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>37</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2</v>
+      </c>
       <c r="AF15" t="n">
         <v>0</v>
       </c>
@@ -4769,49 +5777,49 @@
         <v>1</v>
       </c>
       <c r="BG15" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BI15" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
         <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BO15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP15" t="n">
         <v>7</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BT15" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -4820,15 +5828,19 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>100</v>
-      </c>
-      <c r="BY15" t="inlineStr"/>
-      <c r="BZ15" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>2.33</v>
+      </c>
       <c r="CA15" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="CC15" t="n">
         <v>2.9</v>
@@ -4837,22 +5849,22 @@
         <v>3.11</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="CI15" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="CK15" t="n">
         <v>1.5</v>
@@ -4864,16 +5876,16 @@
         <v>2.4</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="CR15" t="n">
         <v>1.38</v>
@@ -4888,10 +5900,10 @@
         <v>1.43</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX15" t="n">
         <v>1.49</v>
@@ -4906,13 +5918,88 @@
         <v>1.96</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.31</v>
+        <v>3.18</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>88</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>35</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>7</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>6</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>44</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>9</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>19</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="16">
@@ -4922,13 +6009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -4964,112 +6051,112 @@
         <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AM16" t="n">
         <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO16" t="n">
         <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
         <v>12</v>
       </c>
       <c r="AS16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB16" t="n">
         <v>3</v>
       </c>
-      <c r="AT16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>31</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB16" t="n">
+      <c r="BC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG16" t="n">
         <v>4</v>
       </c>
-      <c r="BC16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>5</v>
-      </c>
       <c r="BH16" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BJ16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BM16" t="n">
         <v>0</v>
       </c>
       <c r="BN16" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
@@ -5081,10 +6168,10 @@
         <v>100</v>
       </c>
       <c r="BU16" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV16" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
@@ -5095,81 +6182,81 @@
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="inlineStr"/>
       <c r="CA16" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.62</v>
+        <v>4.58</v>
       </c>
       <c r="CC16" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.58</v>
+        <v>5.68</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="CI16" t="n">
         <v>2.1</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CR16" t="inlineStr"/>
       <c r="CS16" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CT16" t="inlineStr"/>
       <c r="CU16" t="n">
         <v>1.62</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CW16" t="n">
         <v>1.7</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY16" t="n">
         <v>1.96</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="DB16" t="n">
         <v>1.19</v>
@@ -5180,6 +6267,31 @@
       <c r="DD16" t="n">
         <v>2.51</v>
       </c>
+      <c r="DE16" t="inlineStr"/>
+      <c r="DF16" t="inlineStr"/>
+      <c r="DG16" t="inlineStr"/>
+      <c r="DH16" t="inlineStr"/>
+      <c r="DI16" t="inlineStr"/>
+      <c r="DJ16" t="inlineStr"/>
+      <c r="DK16" t="inlineStr"/>
+      <c r="DL16" t="inlineStr"/>
+      <c r="DM16" t="inlineStr"/>
+      <c r="DN16" t="inlineStr"/>
+      <c r="DO16" t="inlineStr"/>
+      <c r="DP16" t="inlineStr"/>
+      <c r="DQ16" t="inlineStr"/>
+      <c r="DR16" t="inlineStr"/>
+      <c r="DS16" t="inlineStr"/>
+      <c r="DT16" t="inlineStr"/>
+      <c r="DU16" t="inlineStr"/>
+      <c r="DV16" t="inlineStr"/>
+      <c r="DW16" t="inlineStr"/>
+      <c r="DX16" t="inlineStr"/>
+      <c r="DY16" t="inlineStr"/>
+      <c r="DZ16" t="inlineStr"/>
+      <c r="EA16" t="inlineStr"/>
+      <c r="EB16" t="inlineStr"/>
+      <c r="EC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5188,13 +6300,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -5277,86 +6389,140 @@
       <c r="AE17" t="n">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>69</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>35</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>51</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>2</v>
+      </c>
       <c r="BG17" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="BJ17" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BM17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO17" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="BP17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ17" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="BR17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BS17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BT17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>1.57</v>
@@ -5365,51 +6531,55 @@
         <v>1.54</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.4</v>
+        <v>4.11</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="CC17" t="inlineStr"/>
-      <c r="CD17" t="inlineStr"/>
+        <v>4.04</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>2.67</v>
+      </c>
       <c r="CE17" t="n">
         <v>1.27</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL17" t="n">
         <v>1.87</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="CR17" t="inlineStr"/>
       <c r="CS17" t="n">
@@ -5420,31 +6590,106 @@
         <v>1.6</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="CX17" t="n">
         <v>1.56</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>53</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>10</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -5454,13 +6699,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -5493,200 +6738,200 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI18" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>33</v>
+        <v>36.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP18" t="n">
         <v>1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AR18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BQ18" t="n">
         <v>4</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>45</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>3</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>2</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BT18" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU18" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV18" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="inlineStr"/>
       <c r="CA18" t="n">
-        <v>4.4</v>
+        <v>4.22</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.56</v>
+        <v>4.24</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.9</v>
+        <v>4.71</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.68</v>
+        <v>4.86</v>
       </c>
       <c r="CE18" t="n">
         <v>1.27</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="CG18" t="n">
         <v>3.4</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CI18" t="n">
         <v>2.25</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO18" t="n">
         <v>1.15</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="CR18" t="inlineStr"/>
       <c r="CS18" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="CT18" t="inlineStr"/>
       <c r="CU18" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CW18" t="n">
         <v>1.68</v>
@@ -5698,20 +6943,45 @@
         <v>1.97</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.47</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="DE18" t="inlineStr"/>
+      <c r="DF18" t="inlineStr"/>
+      <c r="DG18" t="inlineStr"/>
+      <c r="DH18" t="inlineStr"/>
+      <c r="DI18" t="inlineStr"/>
+      <c r="DJ18" t="inlineStr"/>
+      <c r="DK18" t="inlineStr"/>
+      <c r="DL18" t="inlineStr"/>
+      <c r="DM18" t="inlineStr"/>
+      <c r="DN18" t="inlineStr"/>
+      <c r="DO18" t="inlineStr"/>
+      <c r="DP18" t="inlineStr"/>
+      <c r="DQ18" t="inlineStr"/>
+      <c r="DR18" t="inlineStr"/>
+      <c r="DS18" t="inlineStr"/>
+      <c r="DT18" t="inlineStr"/>
+      <c r="DU18" t="inlineStr"/>
+      <c r="DV18" t="inlineStr"/>
+      <c r="DW18" t="inlineStr"/>
+      <c r="DX18" t="inlineStr"/>
+      <c r="DY18" t="inlineStr"/>
+      <c r="DZ18" t="inlineStr"/>
+      <c r="EA18" t="inlineStr"/>
+      <c r="EB18" t="inlineStr"/>
+      <c r="EC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5982,6 +7252,31 @@
       <c r="DD19" t="n">
         <v>2.86</v>
       </c>
+      <c r="DE19" t="inlineStr"/>
+      <c r="DF19" t="inlineStr"/>
+      <c r="DG19" t="inlineStr"/>
+      <c r="DH19" t="inlineStr"/>
+      <c r="DI19" t="inlineStr"/>
+      <c r="DJ19" t="inlineStr"/>
+      <c r="DK19" t="inlineStr"/>
+      <c r="DL19" t="inlineStr"/>
+      <c r="DM19" t="inlineStr"/>
+      <c r="DN19" t="inlineStr"/>
+      <c r="DO19" t="inlineStr"/>
+      <c r="DP19" t="inlineStr"/>
+      <c r="DQ19" t="inlineStr"/>
+      <c r="DR19" t="inlineStr"/>
+      <c r="DS19" t="inlineStr"/>
+      <c r="DT19" t="inlineStr"/>
+      <c r="DU19" t="inlineStr"/>
+      <c r="DV19" t="inlineStr"/>
+      <c r="DW19" t="inlineStr"/>
+      <c r="DX19" t="inlineStr"/>
+      <c r="DY19" t="inlineStr"/>
+      <c r="DZ19" t="inlineStr"/>
+      <c r="EA19" t="inlineStr"/>
+      <c r="EB19" t="inlineStr"/>
+      <c r="EC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5990,41 +7285,95 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>130</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>19</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>65</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2</v>
+      </c>
       <c r="AF20" t="n">
         <v>1</v>
       </c>
@@ -6107,19 +7456,19 @@
         <v>2</v>
       </c>
       <c r="BG20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BH20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BI20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ20" t="n">
         <v>0</v>
       </c>
       <c r="BK20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL20" t="n">
         <v>1</v>
@@ -6131,22 +7480,22 @@
         <v>1</v>
       </c>
       <c r="BO20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP20" t="n">
         <v>6</v>
       </c>
       <c r="BQ20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BT20" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU20" t="n">
         <v>0</v>
@@ -6158,15 +7507,19 @@
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>100</v>
-      </c>
-      <c r="BY20" t="inlineStr"/>
-      <c r="BZ20" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1.88</v>
+      </c>
       <c r="CA20" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="CC20" t="n">
         <v>3.8</v>
@@ -6175,82 +7528,157 @@
         <v>4.3</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CG20" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="CI20" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="CQ20" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="CR20" t="n">
         <v>1.35</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="CT20" t="n">
         <v>3.26</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CV20" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="DC20" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>125</v>
+      </c>
+      <c r="DI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ20" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM20" t="n">
+        <v>76</v>
+      </c>
+      <c r="DN20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DP20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="DQ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="DR20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV20" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="DW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX20" t="n">
+        <v>17</v>
+      </c>
+      <c r="DY20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="DZ20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="EA20" t="n">
+        <v>22</v>
+      </c>
+      <c r="EB20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="EC20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -6522,6 +7950,31 @@
       <c r="DD21" t="n">
         <v>2.53</v>
       </c>
+      <c r="DE21" t="inlineStr"/>
+      <c r="DF21" t="inlineStr"/>
+      <c r="DG21" t="inlineStr"/>
+      <c r="DH21" t="inlineStr"/>
+      <c r="DI21" t="inlineStr"/>
+      <c r="DJ21" t="inlineStr"/>
+      <c r="DK21" t="inlineStr"/>
+      <c r="DL21" t="inlineStr"/>
+      <c r="DM21" t="inlineStr"/>
+      <c r="DN21" t="inlineStr"/>
+      <c r="DO21" t="inlineStr"/>
+      <c r="DP21" t="inlineStr"/>
+      <c r="DQ21" t="inlineStr"/>
+      <c r="DR21" t="inlineStr"/>
+      <c r="DS21" t="inlineStr"/>
+      <c r="DT21" t="inlineStr"/>
+      <c r="DU21" t="inlineStr"/>
+      <c r="DV21" t="inlineStr"/>
+      <c r="DW21" t="inlineStr"/>
+      <c r="DX21" t="inlineStr"/>
+      <c r="DY21" t="inlineStr"/>
+      <c r="DZ21" t="inlineStr"/>
+      <c r="EA21" t="inlineStr"/>
+      <c r="EB21" t="inlineStr"/>
+      <c r="EC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6792,6 +8245,31 @@
       <c r="DD22" t="n">
         <v>4</v>
       </c>
+      <c r="DE22" t="inlineStr"/>
+      <c r="DF22" t="inlineStr"/>
+      <c r="DG22" t="inlineStr"/>
+      <c r="DH22" t="inlineStr"/>
+      <c r="DI22" t="inlineStr"/>
+      <c r="DJ22" t="inlineStr"/>
+      <c r="DK22" t="inlineStr"/>
+      <c r="DL22" t="inlineStr"/>
+      <c r="DM22" t="inlineStr"/>
+      <c r="DN22" t="inlineStr"/>
+      <c r="DO22" t="inlineStr"/>
+      <c r="DP22" t="inlineStr"/>
+      <c r="DQ22" t="inlineStr"/>
+      <c r="DR22" t="inlineStr"/>
+      <c r="DS22" t="inlineStr"/>
+      <c r="DT22" t="inlineStr"/>
+      <c r="DU22" t="inlineStr"/>
+      <c r="DV22" t="inlineStr"/>
+      <c r="DW22" t="inlineStr"/>
+      <c r="DX22" t="inlineStr"/>
+      <c r="DY22" t="inlineStr"/>
+      <c r="DZ22" t="inlineStr"/>
+      <c r="EA22" t="inlineStr"/>
+      <c r="EB22" t="inlineStr"/>
+      <c r="EC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6800,13 +8278,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -6889,47 +8367,101 @@
       <c r="AE23" t="n">
         <v>1</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr"/>
-      <c r="BA23" t="inlineStr"/>
-      <c r="BB23" t="inlineStr"/>
-      <c r="BC23" t="inlineStr"/>
-      <c r="BD23" t="inlineStr"/>
-      <c r="BE23" t="inlineStr"/>
-      <c r="BF23" t="inlineStr"/>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>83</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>35</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>2</v>
+      </c>
       <c r="BG23" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BI23" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BJ23" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL23" t="n">
         <v>1</v>
@@ -6941,13 +8473,13 @@
         <v>1</v>
       </c>
       <c r="BO23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP23" t="n">
         <v>4</v>
       </c>
-      <c r="BP23" t="n">
-        <v>9</v>
-      </c>
       <c r="BQ23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BR23" t="n">
         <v>100</v>
@@ -6956,19 +8488,19 @@
         <v>100</v>
       </c>
       <c r="BT23" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU23" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV23" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BW23" t="n">
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY23" t="n">
         <v>2.5</v>
@@ -6977,51 +8509,55 @@
         <v>2.83</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="CC23" t="inlineStr"/>
-      <c r="CD23" t="inlineStr"/>
+        <v>3.76</v>
+      </c>
+      <c r="CC23" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CD23" t="n">
+        <v>3.26</v>
+      </c>
       <c r="CE23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF23" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CG23" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="CH23" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CI23" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="CJ23" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="CK23" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="CL23" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="CM23" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="CN23" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="CO23" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP23" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="CQ23" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="CR23" t="inlineStr"/>
       <c r="CS23" t="n">
@@ -7032,26 +8568,107 @@
         <v>1.62</v>
       </c>
       <c r="CV23" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="CW23" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CX23" t="n">
         <v>1.56</v>
       </c>
       <c r="CY23" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="CZ23" t="n">
         <v>2.33</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="DB23" t="inlineStr"/>
-      <c r="DC23" t="inlineStr"/>
-      <c r="DD23" t="inlineStr"/>
+        <v>1.98</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DC23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DD23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="DI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DK23" t="n">
+        <v>6</v>
+      </c>
+      <c r="DL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM23" t="n">
+        <v>36</v>
+      </c>
+      <c r="DN23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP23" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="DQ23" t="n">
+        <v>9</v>
+      </c>
+      <c r="DR23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="DS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV23" t="n">
+        <v>46</v>
+      </c>
+      <c r="DW23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DX23" t="n">
+        <v>12</v>
+      </c>
+      <c r="DY23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DZ23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="EA23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="EB23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="EC23" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7060,41 +8677,95 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>64</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>32</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>10</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>39</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>3</v>
+      </c>
       <c r="AF24" t="n">
         <v>0</v>
       </c>
@@ -7177,16 +8848,16 @@
         <v>3</v>
       </c>
       <c r="BG24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH24" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BI24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BK24" t="n">
         <v>0</v>
@@ -7195,28 +8866,28 @@
         <v>1</v>
       </c>
       <c r="BM24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BO24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BP24" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BR24" t="n">
         <v>100</v>
       </c>
       <c r="BS24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BT24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU24" t="n">
         <v>0</v>
@@ -7228,15 +8899,19 @@
         <v>0</v>
       </c>
       <c r="BX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY24" t="inlineStr"/>
-      <c r="BZ24" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>3.41</v>
+      </c>
       <c r="CA24" t="n">
-        <v>4.7</v>
+        <v>4.08</v>
       </c>
       <c r="CB24" t="n">
-        <v>5.78</v>
+        <v>4.63</v>
       </c>
       <c r="CC24" t="n">
         <v>6.55</v>
@@ -7245,53 +8920,53 @@
         <v>8.640000000000001</v>
       </c>
       <c r="CE24" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="CF24" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="CG24" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="CH24" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="CI24" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CJ24" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK24" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CL24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CM24" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CN24" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CP24" t="n">
         <v>1.7</v>
       </c>
-      <c r="CM24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="CN24" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="CP24" t="n">
-        <v>1.47</v>
-      </c>
       <c r="CQ24" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="CR24" t="inlineStr"/>
       <c r="CS24" t="inlineStr"/>
       <c r="CT24" t="inlineStr"/>
       <c r="CU24" t="inlineStr"/>
       <c r="CV24" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CW24" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CX24" t="n">
         <v>1.46</v>
@@ -7306,13 +8981,88 @@
         <v>1.99</v>
       </c>
       <c r="DB24" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="DC24" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="DD24" t="n">
-        <v>2.11</v>
+        <v>2.72</v>
+      </c>
+      <c r="DE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF24" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DH24" t="n">
+        <v>76</v>
+      </c>
+      <c r="DI24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DJ24" t="n">
+        <v>3</v>
+      </c>
+      <c r="DK24" t="n">
+        <v>5</v>
+      </c>
+      <c r="DL24" t="n">
+        <v>2</v>
+      </c>
+      <c r="DM24" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="DN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DP24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="DQ24" t="n">
+        <v>11</v>
+      </c>
+      <c r="DR24" t="n">
+        <v>9</v>
+      </c>
+      <c r="DS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV24" t="n">
+        <v>40</v>
+      </c>
+      <c r="DW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX24" t="n">
+        <v>13</v>
+      </c>
+      <c r="DY24" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="DZ24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="EA24" t="n">
+        <v>17</v>
+      </c>
+      <c r="EB24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="EC24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -7322,10 +9072,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -7334,13 +9084,13 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="H25" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -7349,64 +9099,64 @@
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O25" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="P25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
         <v>14</v>
       </c>
-      <c r="Q25" t="n">
-        <v>12</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>44</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>17</v>
-      </c>
       <c r="AA25" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -7439,16 +9189,16 @@
       <c r="BE25" t="inlineStr"/>
       <c r="BF25" t="inlineStr"/>
       <c r="BG25" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BH25" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="BI25" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BJ25" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BK25" t="n">
         <v>0</v>
@@ -7463,13 +9213,13 @@
         <v>1</v>
       </c>
       <c r="BO25" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BP25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BQ25" t="n">
         <v>8</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>10</v>
       </c>
       <c r="BR25" t="n">
         <v>100</v>
@@ -7478,7 +9228,7 @@
         <v>100</v>
       </c>
       <c r="BT25" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU25" t="n">
         <v>0</v>
@@ -7493,83 +9243,83 @@
         <v>0</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="CA25" t="n">
-        <v>4.3</v>
+        <v>3.97</v>
       </c>
       <c r="CB25" t="n">
-        <v>4.37</v>
+        <v>4.02</v>
       </c>
       <c r="CC25" t="inlineStr"/>
       <c r="CD25" t="inlineStr"/>
       <c r="CE25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="CF25" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="CG25" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="CH25" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="CI25" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="CJ25" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="CK25" t="n">
         <v>1.42</v>
       </c>
       <c r="CL25" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="CM25" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CN25" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="CO25" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="CP25" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="CQ25" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="CR25" t="inlineStr"/>
       <c r="CS25" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="CT25" t="inlineStr"/>
       <c r="CU25" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="CV25" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="CW25" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="CX25" t="n">
         <v>1.74</v>
       </c>
       <c r="CY25" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="CZ25" t="n">
         <v>2.05</v>
       </c>
       <c r="DA25" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="DB25" t="n">
         <v>1.14</v>
@@ -7580,6 +9330,31 @@
       <c r="DD25" t="n">
         <v>2.15</v>
       </c>
+      <c r="DE25" t="inlineStr"/>
+      <c r="DF25" t="inlineStr"/>
+      <c r="DG25" t="inlineStr"/>
+      <c r="DH25" t="inlineStr"/>
+      <c r="DI25" t="inlineStr"/>
+      <c r="DJ25" t="inlineStr"/>
+      <c r="DK25" t="inlineStr"/>
+      <c r="DL25" t="inlineStr"/>
+      <c r="DM25" t="inlineStr"/>
+      <c r="DN25" t="inlineStr"/>
+      <c r="DO25" t="inlineStr"/>
+      <c r="DP25" t="inlineStr"/>
+      <c r="DQ25" t="inlineStr"/>
+      <c r="DR25" t="inlineStr"/>
+      <c r="DS25" t="inlineStr"/>
+      <c r="DT25" t="inlineStr"/>
+      <c r="DU25" t="inlineStr"/>
+      <c r="DV25" t="inlineStr"/>
+      <c r="DW25" t="inlineStr"/>
+      <c r="DX25" t="inlineStr"/>
+      <c r="DY25" t="inlineStr"/>
+      <c r="DZ25" t="inlineStr"/>
+      <c r="EA25" t="inlineStr"/>
+      <c r="EB25" t="inlineStr"/>
+      <c r="EC25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7846,6 +9621,31 @@
       <c r="DD26" t="n">
         <v>2.51</v>
       </c>
+      <c r="DE26" t="inlineStr"/>
+      <c r="DF26" t="inlineStr"/>
+      <c r="DG26" t="inlineStr"/>
+      <c r="DH26" t="inlineStr"/>
+      <c r="DI26" t="inlineStr"/>
+      <c r="DJ26" t="inlineStr"/>
+      <c r="DK26" t="inlineStr"/>
+      <c r="DL26" t="inlineStr"/>
+      <c r="DM26" t="inlineStr"/>
+      <c r="DN26" t="inlineStr"/>
+      <c r="DO26" t="inlineStr"/>
+      <c r="DP26" t="inlineStr"/>
+      <c r="DQ26" t="inlineStr"/>
+      <c r="DR26" t="inlineStr"/>
+      <c r="DS26" t="inlineStr"/>
+      <c r="DT26" t="inlineStr"/>
+      <c r="DU26" t="inlineStr"/>
+      <c r="DV26" t="inlineStr"/>
+      <c r="DW26" t="inlineStr"/>
+      <c r="DX26" t="inlineStr"/>
+      <c r="DY26" t="inlineStr"/>
+      <c r="DZ26" t="inlineStr"/>
+      <c r="EA26" t="inlineStr"/>
+      <c r="EB26" t="inlineStr"/>
+      <c r="EC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7854,13 +9654,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -7943,41 +9743,95 @@
       <c r="AE27" t="n">
         <v>2</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="inlineStr"/>
-      <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr"/>
-      <c r="AX27" t="inlineStr"/>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr"/>
-      <c r="BA27" t="inlineStr"/>
-      <c r="BB27" t="inlineStr"/>
-      <c r="BC27" t="inlineStr"/>
-      <c r="BD27" t="inlineStr"/>
-      <c r="BE27" t="inlineStr"/>
-      <c r="BF27" t="inlineStr"/>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>123</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>61</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1</v>
+      </c>
       <c r="BG27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BH27" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BI27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BJ27" t="n">
         <v>1</v>
@@ -7989,19 +9843,19 @@
         <v>1</v>
       </c>
       <c r="BM27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BN27" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BO27" t="n">
         <v>1</v>
       </c>
       <c r="BP27" t="n">
-        <v>-1</v>
+        <v>3.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BR27" t="n">
         <v>100</v>
@@ -8010,7 +9864,7 @@
         <v>100</v>
       </c>
       <c r="BT27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU27" t="n">
         <v>0</v>
@@ -8022,7 +9876,7 @@
         <v>0</v>
       </c>
       <c r="BX27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY27" t="n">
         <v>1.3</v>
@@ -8031,51 +9885,55 @@
         <v>1.35</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.65</v>
+        <v>4.06</v>
       </c>
       <c r="CB27" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="CC27" t="inlineStr"/>
-      <c r="CD27" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="CC27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CD27" t="n">
+        <v>2.21</v>
+      </c>
       <c r="CE27" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="CF27" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="CG27" t="n">
-        <v>3.5</v>
+        <v>3.19</v>
       </c>
       <c r="CH27" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="CI27" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CK27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CL27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CM27" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CN27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CO27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CP27" t="n">
         <v>1.74</v>
       </c>
-      <c r="CK27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CL27" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CM27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="CN27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CO27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="CP27" t="n">
-        <v>1.56</v>
-      </c>
       <c r="CQ27" t="n">
-        <v>2.32</v>
+        <v>2.78</v>
       </c>
       <c r="CR27" t="inlineStr"/>
       <c r="CS27" t="n">
@@ -8100,13 +9958,88 @@
         <v>2.11</v>
       </c>
       <c r="DB27" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="DC27" t="n">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="DD27" t="n">
-        <v>2.17</v>
+        <v>2.75</v>
+      </c>
+      <c r="DE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH27" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="DI27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DJ27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DK27" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL27" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DM27" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="DN27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DP27" t="n">
+        <v>8</v>
+      </c>
+      <c r="DQ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="DR27" t="n">
+        <v>6</v>
+      </c>
+      <c r="DS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV27" t="n">
+        <v>52</v>
+      </c>
+      <c r="DW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="DY27" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="DZ27" t="n">
+        <v>6</v>
+      </c>
+      <c r="EA27" t="n">
+        <v>21</v>
+      </c>
+      <c r="EB27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="EC27" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="28">
@@ -8116,41 +10049,95 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>67</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>29</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>13</v>
+      </c>
+      <c r="R28" t="n">
+        <v>5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
       <c r="AF28" t="n">
         <v>0</v>
       </c>
@@ -8233,37 +10220,37 @@
         <v>0</v>
       </c>
       <c r="BG28" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BH28" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BI28" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BJ28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BL28" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BN28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO28" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BP28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BQ28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BR28" t="n">
         <v>100</v>
@@ -8275,7 +10262,7 @@
         <v>100</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BV28" t="n">
         <v>0</v>
@@ -8284,15 +10271,19 @@
         <v>0</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY28" t="inlineStr"/>
-      <c r="BZ28" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>4.6</v>
+      </c>
       <c r="CA28" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="CB28" t="n">
-        <v>4.37</v>
+        <v>4.43</v>
       </c>
       <c r="CC28" t="n">
         <v>3.9</v>
@@ -8301,43 +10292,43 @@
         <v>4.17</v>
       </c>
       <c r="CE28" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CF28" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="CG28" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="CH28" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CI28" t="n">
         <v>2.5</v>
       </c>
       <c r="CJ28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CK28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CL28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CM28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CN28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CO28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CP28" t="n">
         <v>1.42</v>
       </c>
-      <c r="CK28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CL28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CM28" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="CN28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CO28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CP28" t="n">
-        <v>1.4</v>
-      </c>
       <c r="CQ28" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="CR28" t="inlineStr"/>
       <c r="CS28" t="n">
@@ -8348,22 +10339,22 @@
         <v>1.71</v>
       </c>
       <c r="CV28" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="CW28" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CX28" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="CY28" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CZ28" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="DA28" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="DB28" t="n">
         <v>1.14</v>
@@ -8372,7 +10363,82 @@
         <v>1.46</v>
       </c>
       <c r="DD28" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
+      </c>
+      <c r="DE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG28" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH28" t="n">
+        <v>75</v>
+      </c>
+      <c r="DI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DK28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DL28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM28" t="n">
+        <v>33</v>
+      </c>
+      <c r="DN28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DP28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="DQ28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="DR28" t="n">
+        <v>5</v>
+      </c>
+      <c r="DS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV28" t="n">
+        <v>49</v>
+      </c>
+      <c r="DW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DY28" t="n">
+        <v>5</v>
+      </c>
+      <c r="DZ28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="EA28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="EB28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="EC28" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="29">
@@ -8632,6 +10698,31 @@
       <c r="DD29" t="n">
         <v>2.66</v>
       </c>
+      <c r="DE29" t="inlineStr"/>
+      <c r="DF29" t="inlineStr"/>
+      <c r="DG29" t="inlineStr"/>
+      <c r="DH29" t="inlineStr"/>
+      <c r="DI29" t="inlineStr"/>
+      <c r="DJ29" t="inlineStr"/>
+      <c r="DK29" t="inlineStr"/>
+      <c r="DL29" t="inlineStr"/>
+      <c r="DM29" t="inlineStr"/>
+      <c r="DN29" t="inlineStr"/>
+      <c r="DO29" t="inlineStr"/>
+      <c r="DP29" t="inlineStr"/>
+      <c r="DQ29" t="inlineStr"/>
+      <c r="DR29" t="inlineStr"/>
+      <c r="DS29" t="inlineStr"/>
+      <c r="DT29" t="inlineStr"/>
+      <c r="DU29" t="inlineStr"/>
+      <c r="DV29" t="inlineStr"/>
+      <c r="DW29" t="inlineStr"/>
+      <c r="DX29" t="inlineStr"/>
+      <c r="DY29" t="inlineStr"/>
+      <c r="DZ29" t="inlineStr"/>
+      <c r="EA29" t="inlineStr"/>
+      <c r="EB29" t="inlineStr"/>
+      <c r="EC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8640,13 +10731,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
@@ -8679,49 +10770,49 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI30" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AO30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AT30" t="n">
         <v>3</v>
       </c>
       <c r="AU30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV30" t="n">
         <v>0</v>
@@ -8733,61 +10824,61 @@
         <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>55</v>
+        <v>47.5</v>
       </c>
       <c r="AZ30" t="n">
         <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD30" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.48</v>
+        <v>1.1</v>
       </c>
       <c r="BF30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BH30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BI30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BJ30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BL30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BM30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO30" t="n">
         <v>3</v>
       </c>
       <c r="BP30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BQ30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BR30" t="n">
         <v>100</v>
@@ -8799,109 +10890,134 @@
         <v>100</v>
       </c>
       <c r="BU30" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV30" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BW30" t="n">
         <v>0</v>
       </c>
       <c r="BX30" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="inlineStr"/>
       <c r="CA30" t="n">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="CB30" t="n">
-        <v>3.66</v>
+        <v>4.36</v>
       </c>
       <c r="CC30" t="n">
-        <v>3.7</v>
+        <v>4.62</v>
       </c>
       <c r="CD30" t="n">
-        <v>3.73</v>
+        <v>5.78</v>
       </c>
       <c r="CE30" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="CF30" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CG30" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="CH30" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="CI30" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="CJ30" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CK30" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CL30" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="CM30" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="CN30" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="CO30" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="CP30" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="CQ30" t="n">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="CR30" t="n">
         <v>1.34</v>
       </c>
       <c r="CS30" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="CT30" t="n">
         <v>3.36</v>
       </c>
       <c r="CU30" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="CV30" t="n">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="CW30" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="CX30" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY30" t="n">
         <v>1.9</v>
       </c>
       <c r="CZ30" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DA30" t="n">
         <v>1.9</v>
       </c>
       <c r="DB30" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="DC30" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="DD30" t="n">
-        <v>2.89</v>
-      </c>
+        <v>2.66</v>
+      </c>
+      <c r="DE30" t="inlineStr"/>
+      <c r="DF30" t="inlineStr"/>
+      <c r="DG30" t="inlineStr"/>
+      <c r="DH30" t="inlineStr"/>
+      <c r="DI30" t="inlineStr"/>
+      <c r="DJ30" t="inlineStr"/>
+      <c r="DK30" t="inlineStr"/>
+      <c r="DL30" t="inlineStr"/>
+      <c r="DM30" t="inlineStr"/>
+      <c r="DN30" t="inlineStr"/>
+      <c r="DO30" t="inlineStr"/>
+      <c r="DP30" t="inlineStr"/>
+      <c r="DQ30" t="inlineStr"/>
+      <c r="DR30" t="inlineStr"/>
+      <c r="DS30" t="inlineStr"/>
+      <c r="DT30" t="inlineStr"/>
+      <c r="DU30" t="inlineStr"/>
+      <c r="DV30" t="inlineStr"/>
+      <c r="DW30" t="inlineStr"/>
+      <c r="DX30" t="inlineStr"/>
+      <c r="DY30" t="inlineStr"/>
+      <c r="DZ30" t="inlineStr"/>
+      <c r="EA30" t="inlineStr"/>
+      <c r="EB30" t="inlineStr"/>
+      <c r="EC30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8910,10 +11026,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -8922,82 +11038,82 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="H31" t="n">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>47</v>
+        <v>42.5</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P31" t="n">
         <v>11</v>
       </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>59</v>
+        <v>59.5</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="AE31" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
@@ -9027,46 +11143,46 @@
       <c r="BE31" t="inlineStr"/>
       <c r="BF31" t="inlineStr"/>
       <c r="BG31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH31" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BI31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BK31" t="n">
         <v>0</v>
       </c>
       <c r="BL31" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BM31" t="n">
         <v>0</v>
       </c>
       <c r="BN31" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BO31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BP31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BR31" t="n">
         <v>100</v>
       </c>
       <c r="BS31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BT31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU31" t="n">
         <v>0</v>
@@ -9081,89 +11197,118 @@
         <v>0</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BZ31" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="CA31" t="n">
-        <v>4.7</v>
+        <v>4.63</v>
       </c>
       <c r="CB31" t="n">
-        <v>5.78</v>
+        <v>5.43</v>
       </c>
       <c r="CC31" t="inlineStr"/>
       <c r="CD31" t="inlineStr"/>
       <c r="CE31" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="CF31" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CG31" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="CH31" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CI31" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CJ31" t="n">
         <v>1.65</v>
       </c>
       <c r="CK31" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CL31" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CM31" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CN31" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CO31" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP31" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="CQ31" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CR31" t="inlineStr"/>
-      <c r="CS31" t="inlineStr"/>
+      <c r="CS31" t="n">
+        <v>2.39</v>
+      </c>
       <c r="CT31" t="inlineStr"/>
-      <c r="CU31" t="inlineStr"/>
+      <c r="CU31" t="n">
+        <v>1.61</v>
+      </c>
       <c r="CV31" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="CW31" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="CX31" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CY31" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="CZ31" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="DA31" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="DB31" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="DC31" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.11</v>
-      </c>
+        <v>2.27</v>
+      </c>
+      <c r="DE31" t="inlineStr"/>
+      <c r="DF31" t="inlineStr"/>
+      <c r="DG31" t="inlineStr"/>
+      <c r="DH31" t="inlineStr"/>
+      <c r="DI31" t="inlineStr"/>
+      <c r="DJ31" t="inlineStr"/>
+      <c r="DK31" t="inlineStr"/>
+      <c r="DL31" t="inlineStr"/>
+      <c r="DM31" t="inlineStr"/>
+      <c r="DN31" t="inlineStr"/>
+      <c r="DO31" t="inlineStr"/>
+      <c r="DP31" t="inlineStr"/>
+      <c r="DQ31" t="inlineStr"/>
+      <c r="DR31" t="inlineStr"/>
+      <c r="DS31" t="inlineStr"/>
+      <c r="DT31" t="inlineStr"/>
+      <c r="DU31" t="inlineStr"/>
+      <c r="DV31" t="inlineStr"/>
+      <c r="DW31" t="inlineStr"/>
+      <c r="DX31" t="inlineStr"/>
+      <c r="DY31" t="inlineStr"/>
+      <c r="DZ31" t="inlineStr"/>
+      <c r="EA31" t="inlineStr"/>
+      <c r="EB31" t="inlineStr"/>
+      <c r="EC31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
@@ -1448,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AR2" t="n">
         <v>9.5</v>
@@ -1670,61 +1670,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>105</v>
+        <v>96.5</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>52.5</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>17</v>
+      </c>
+      <c r="R3" t="n">
         <v>8</v>
       </c>
-      <c r="Q3" t="n">
-        <v>16</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6</v>
-      </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1736,28 +1736,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>57</v>
+        <v>55.5</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AC3" t="n">
         <v>17</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
@@ -1787,34 +1787,34 @@
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BQ3" t="n">
         <v>8</v>
@@ -1823,13 +1823,13 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BT3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -1838,19 +1838,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="CC3" t="inlineStr"/>
       <c r="CD3" t="inlineStr"/>
@@ -1858,40 +1858,40 @@
         <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI3" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -1906,31 +1906,31 @@
         <v>1.43</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="DE3" t="inlineStr"/>
       <c r="DF3" t="inlineStr"/>
@@ -2147,7 +2147,7 @@
         <v>2.92</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="CE4" t="n">
         <v>1.28</v>
@@ -2196,7 +2196,7 @@
         <v>2.46</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CX4" t="inlineStr"/>
       <c r="CY4" t="n">
@@ -2207,13 +2207,13 @@
         <v>2.05</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC4" t="n">
         <v>1.68</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="DE4" t="inlineStr"/>
       <c r="DF4" t="inlineStr"/>
@@ -2689,7 +2689,7 @@
         <v>-1</v>
       </c>
       <c r="P6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
         <v>15</v>
@@ -2719,19 +2719,19 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
         <v>15</v>
       </c>
       <c r="AB6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
         <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -2993,7 +2993,7 @@
         <v>-1</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="DQ6" t="n">
         <v>12.5</v>
@@ -3017,19 +3017,19 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="DY6" t="n">
         <v>10</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="EA6" t="n">
         <v>17.5</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="EC6" t="n">
         <v>3</v>
@@ -3333,13 +3333,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3422,65 +3422,119 @@
       <c r="AE8" t="n">
         <v>1</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>87</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>49</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3</v>
+      </c>
       <c r="BG8" t="n">
         <v>1</v>
       </c>
       <c r="BH8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>6</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>4</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -3510,51 +3564,55 @@
         <v>2.94</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="CC8" t="inlineStr"/>
-      <c r="CD8" t="inlineStr"/>
+        <v>3.42</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>4.13</v>
+      </c>
       <c r="CE8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="CG8" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="CN8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="CO8" t="n">
         <v>1.25</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="CR8" t="n">
         <v>1.44</v>
@@ -3569,57 +3627,107 @@
         <v>1.37</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DA8" t="n">
         <v>2</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="DD8" t="n">
-        <v>4</v>
-      </c>
-      <c r="DE8" t="inlineStr"/>
-      <c r="DF8" t="inlineStr"/>
-      <c r="DG8" t="inlineStr"/>
-      <c r="DH8" t="inlineStr"/>
-      <c r="DI8" t="inlineStr"/>
-      <c r="DJ8" t="inlineStr"/>
-      <c r="DK8" t="inlineStr"/>
-      <c r="DL8" t="inlineStr"/>
-      <c r="DM8" t="inlineStr"/>
-      <c r="DN8" t="inlineStr"/>
-      <c r="DO8" t="inlineStr"/>
-      <c r="DP8" t="inlineStr"/>
-      <c r="DQ8" t="inlineStr"/>
-      <c r="DR8" t="inlineStr"/>
-      <c r="DS8" t="inlineStr"/>
-      <c r="DT8" t="inlineStr"/>
-      <c r="DU8" t="inlineStr"/>
-      <c r="DV8" t="inlineStr"/>
-      <c r="DW8" t="inlineStr"/>
-      <c r="DX8" t="inlineStr"/>
-      <c r="DY8" t="inlineStr"/>
-      <c r="DZ8" t="inlineStr"/>
-      <c r="EA8" t="inlineStr"/>
-      <c r="EB8" t="inlineStr"/>
-      <c r="EC8" t="inlineStr"/>
+        <v>3.74</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>44</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>5</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>7</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>24</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4054,7 +4162,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -4072,10 +4180,10 @@
         <v>11.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -4093,25 +4201,25 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AB10" t="n">
         <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -4147,7 +4255,7 @@
         <v>2.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="BI10" t="n">
         <v>2.5</v>
@@ -4617,13 +4725,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -4656,115 +4764,115 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>53.5</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AQ12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR12" t="n">
         <v>15</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>14</v>
       </c>
       <c r="AS12" t="n">
         <v>5</v>
       </c>
       <c r="AT12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN12" t="n">
         <v>3</v>
       </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>68</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>2</v>
-      </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
@@ -4776,104 +4884,104 @@
         <v>100</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="inlineStr"/>
       <c r="BZ12" t="inlineStr"/>
       <c r="CA12" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.09</v>
+        <v>4.23</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.57</v>
+        <v>2.66</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="CF12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CQ12" t="n">
         <v>2.15</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="CH12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CQ12" t="n">
-        <v>2.3</v>
       </c>
       <c r="CR12" t="inlineStr"/>
       <c r="CS12" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="CT12" t="inlineStr"/>
       <c r="CU12" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.84</v>
+        <v>2.97</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="DE12" t="inlineStr"/>
       <c r="DF12" t="inlineStr"/>
@@ -5082,7 +5190,7 @@
         <v>2.33</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CA13" t="n">
         <v>3.72</v>
@@ -5144,10 +5252,10 @@
         <v>1.51</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CX13" t="n">
         <v>1.61</v>
@@ -5162,13 +5270,13 @@
         <v>1.96</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DC13" t="n">
         <v>1.72</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="DE13" t="inlineStr"/>
       <c r="DF13" t="inlineStr"/>
@@ -5329,7 +5437,7 @@
         <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
         <v>4</v>
@@ -5560,7 +5668,7 @@
         <v>13</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="DR14" t="n">
         <v>4</v>
@@ -6408,7 +6516,7 @@
         <v>3</v>
       </c>
       <c r="AL17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM17" t="n">
         <v>-1</v>
@@ -6426,10 +6534,10 @@
         <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
@@ -6447,25 +6555,25 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AZ17" t="n">
         <v>1</v>
       </c>
       <c r="BA17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB17" t="n">
         <v>6</v>
       </c>
-      <c r="BB17" t="n">
-        <v>5</v>
-      </c>
       <c r="BC17" t="n">
         <v>1</v>
       </c>
       <c r="BD17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BF17" t="n">
         <v>2</v>
@@ -6474,7 +6582,7 @@
         <v>2.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BI17" t="n">
         <v>2.5</v>
@@ -6635,7 +6743,7 @@
         <v>1.5</v>
       </c>
       <c r="DK17" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="DL17" t="n">
         <v>0</v>
@@ -6653,10 +6761,10 @@
         <v>12.5</v>
       </c>
       <c r="DQ17" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="DR17" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -6668,25 +6776,25 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="DW17" t="n">
         <v>0.5</v>
       </c>
       <c r="DX17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="DY17" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="DZ17" t="n">
         <v>4.5</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="EC17" t="n">
         <v>1</v>
@@ -6990,13 +7098,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -7029,115 +7137,115 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>110</v>
+        <v>103.5</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL19" t="n">
         <v>3</v>
       </c>
-      <c r="AL19" t="n">
-        <v>2</v>
-      </c>
       <c r="AM19" t="n">
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>77</v>
+        <v>62.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP19" t="n">
         <v>1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>58</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD19" t="n">
         <v>14</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BE19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP19" t="n">
         <v>3</v>
       </c>
-      <c r="AT19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>64</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BF19" t="n">
+      <c r="BQ19" t="n">
         <v>3</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>1</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
@@ -7146,7 +7254,7 @@
         <v>100</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -7166,52 +7274,52 @@
         <v>3.78</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
@@ -7226,31 +7334,31 @@
         <v>1.51</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.86</v>
+        <v>3.18</v>
       </c>
       <c r="DE19" t="inlineStr"/>
       <c r="DF19" t="inlineStr"/>
@@ -7688,10 +7796,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -7700,82 +7808,82 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="H21" t="n">
-        <v>87</v>
+        <v>79.5</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>38</v>
+        <v>32.5</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="R21" t="n">
+        <v>9</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA21" t="n">
         <v>8</v>
       </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>48</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>11</v>
-      </c>
       <c r="AB21" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="AE21" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
@@ -7805,37 +7913,37 @@
       <c r="BE21" t="inlineStr"/>
       <c r="BF21" t="inlineStr"/>
       <c r="BG21" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BI21" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL21" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BM21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BN21" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="BO21" t="n">
         <v>2</v>
       </c>
       <c r="BP21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
@@ -7847,108 +7955,108 @@
         <v>100</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BV21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BX21" t="n">
         <v>100</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.69</v>
+        <v>2.57</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1.81</v>
+        <v>2.99</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.9</v>
+        <v>4.14</v>
       </c>
       <c r="CC21" t="inlineStr"/>
       <c r="CD21" t="inlineStr"/>
       <c r="CE21" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="CG21" t="n">
-        <v>3.1</v>
+        <v>3.49</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="CI21" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="CQ21" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="CR21" t="n">
         <v>1.35</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="CT21" t="n">
         <v>3.26</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="CV21" t="n">
-        <v>2.43</v>
+        <v>2.77</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.53</v>
+        <v>2.26</v>
       </c>
       <c r="DE21" t="inlineStr"/>
       <c r="DF21" t="inlineStr"/>
@@ -7983,41 +8091,95 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>126</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>86</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>13</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2</v>
+      </c>
       <c r="AF22" t="n">
         <v>0</v>
       </c>
@@ -8100,46 +8262,46 @@
         <v>3</v>
       </c>
       <c r="BG22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH22" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="BI22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BL22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BM22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO22" t="n">
         <v>1</v>
       </c>
       <c r="BP22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BR22" t="n">
         <v>100</v>
       </c>
       <c r="BS22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BT22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU22" t="n">
         <v>0</v>
@@ -8151,15 +8313,19 @@
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY22" t="inlineStr"/>
-      <c r="BZ22" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>2.27</v>
+      </c>
       <c r="CA22" t="n">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CC22" t="n">
         <v>2.2</v>
@@ -8168,43 +8334,43 @@
         <v>2.51</v>
       </c>
       <c r="CE22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="CF22" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="CG22" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CH22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CI22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CJ22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CK22" t="n">
         <v>1.48</v>
       </c>
-      <c r="CI22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CJ22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CK22" t="n">
-        <v>1.44</v>
-      </c>
       <c r="CL22" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="CM22" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="CN22" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="CO22" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="CP22" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="CQ22" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="CR22" t="n">
         <v>1.44</v>
@@ -8219,57 +8385,107 @@
         <v>1.37</v>
       </c>
       <c r="CV22" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="CW22" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="CX22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CY22" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="CZ22" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="DA22" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DB22" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DC22" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="DD22" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="DE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF22" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG22" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH22" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="DI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ22" t="n">
         <v>4</v>
       </c>
-      <c r="DE22" t="inlineStr"/>
-      <c r="DF22" t="inlineStr"/>
-      <c r="DG22" t="inlineStr"/>
-      <c r="DH22" t="inlineStr"/>
-      <c r="DI22" t="inlineStr"/>
-      <c r="DJ22" t="inlineStr"/>
-      <c r="DK22" t="inlineStr"/>
-      <c r="DL22" t="inlineStr"/>
-      <c r="DM22" t="inlineStr"/>
-      <c r="DN22" t="inlineStr"/>
-      <c r="DO22" t="inlineStr"/>
-      <c r="DP22" t="inlineStr"/>
-      <c r="DQ22" t="inlineStr"/>
-      <c r="DR22" t="inlineStr"/>
-      <c r="DS22" t="inlineStr"/>
-      <c r="DT22" t="inlineStr"/>
-      <c r="DU22" t="inlineStr"/>
-      <c r="DV22" t="inlineStr"/>
-      <c r="DW22" t="inlineStr"/>
-      <c r="DX22" t="inlineStr"/>
-      <c r="DY22" t="inlineStr"/>
-      <c r="DZ22" t="inlineStr"/>
-      <c r="EA22" t="inlineStr"/>
-      <c r="EB22" t="inlineStr"/>
-      <c r="EC22" t="inlineStr"/>
+      <c r="DK22" t="n">
+        <v>5</v>
+      </c>
+      <c r="DL22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM22" t="n">
+        <v>60</v>
+      </c>
+      <c r="DN22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DO22" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DQ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="DR22" t="n">
+        <v>4</v>
+      </c>
+      <c r="DS22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DT22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV22" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="DW22" t="n">
+        <v>1</v>
+      </c>
+      <c r="DX22" t="n">
+        <v>14</v>
+      </c>
+      <c r="DY22" t="n">
+        <v>10</v>
+      </c>
+      <c r="DZ22" t="n">
+        <v>4</v>
+      </c>
+      <c r="EA22" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="EB22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="EC22" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8401,7 +8617,7 @@
         <v>-1</v>
       </c>
       <c r="AQ23" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AR23" t="n">
         <v>12</v>
@@ -8628,7 +8844,7 @@
         <v>1</v>
       </c>
       <c r="DP23" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="DQ23" t="n">
         <v>9</v>
@@ -8719,7 +8935,7 @@
         <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
         <v>7</v>
@@ -9023,7 +9239,7 @@
         <v>2.5</v>
       </c>
       <c r="DP24" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="DQ24" t="n">
         <v>11</v>
@@ -9114,7 +9330,7 @@
         <v>4.5</v>
       </c>
       <c r="P25" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q25" t="n">
         <v>15.5</v>
@@ -9363,37 +9579,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="H26" t="n">
-        <v>91</v>
+        <v>76.5</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M26" t="n">
         <v>34</v>
@@ -9402,22 +9618,22 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
         <v>9</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -9429,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -9438,19 +9654,19 @@
         <v>10</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
@@ -9480,37 +9696,37 @@
       <c r="BE26" t="inlineStr"/>
       <c r="BF26" t="inlineStr"/>
       <c r="BG26" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BH26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BI26" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BJ26" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BK26" t="n">
         <v>0</v>
       </c>
       <c r="BL26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BM26" t="n">
         <v>0</v>
       </c>
       <c r="BN26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO26" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BP26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BQ26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR26" t="n">
         <v>100</v>
@@ -9519,13 +9735,13 @@
         <v>100</v>
       </c>
       <c r="BT26" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU26" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV26" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BW26" t="n">
         <v>0</v>
@@ -9534,92 +9750,92 @@
         <v>0</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CA26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB26" t="n">
-        <v>4.62</v>
+        <v>4.64</v>
       </c>
       <c r="CC26" t="inlineStr"/>
       <c r="CD26" t="inlineStr"/>
       <c r="CE26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CF26" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="CG26" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="CH26" t="n">
         <v>1.65</v>
       </c>
       <c r="CI26" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="CJ26" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="CK26" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL26" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="CM26" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CN26" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="CO26" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP26" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CQ26" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CR26" t="inlineStr"/>
       <c r="CS26" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="CT26" t="inlineStr"/>
       <c r="CU26" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="CV26" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="CW26" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CX26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CY26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CZ26" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DA26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DB26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DC26" t="n">
         <v>1.57</v>
       </c>
-      <c r="CY26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CZ26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="DA26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="DB26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="DC26" t="n">
-        <v>1.6</v>
-      </c>
       <c r="DD26" t="n">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="DE26" t="inlineStr"/>
       <c r="DF26" t="inlineStr"/>
@@ -9777,7 +9993,7 @@
         <v>6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AR27" t="n">
         <v>9</v>
@@ -10000,7 +10216,7 @@
         <v>2.5</v>
       </c>
       <c r="DP27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="DQ27" t="n">
         <v>13</v>
@@ -10448,13 +10664,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -10537,44 +10753,98 @@
       <c r="AE29" t="n">
         <v>2</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
-      <c r="BA29" t="inlineStr"/>
-      <c r="BB29" t="inlineStr"/>
-      <c r="BC29" t="inlineStr"/>
-      <c r="BD29" t="inlineStr"/>
-      <c r="BE29" t="inlineStr"/>
-      <c r="BF29" t="inlineStr"/>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>52</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>35</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1</v>
+      </c>
       <c r="BG29" t="n">
         <v>2</v>
       </c>
       <c r="BH29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BI29" t="n">
         <v>2</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BK29" t="n">
         <v>0</v>
@@ -10583,19 +10853,19 @@
         <v>1</v>
       </c>
       <c r="BM29" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BP29" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BR29" t="n">
         <v>100</v>
@@ -10616,7 +10886,7 @@
         <v>0</v>
       </c>
       <c r="BX29" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY29" t="n">
         <v>2.16</v>
@@ -10625,104 +10895,166 @@
         <v>2.55</v>
       </c>
       <c r="CA29" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="CB29" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="CC29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="CD29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="CE29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CF29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CG29" t="n">
         <v>3.58</v>
       </c>
-      <c r="CC29" t="inlineStr"/>
-      <c r="CD29" t="inlineStr"/>
-      <c r="CE29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CF29" t="n">
+      <c r="CH29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CI29" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CJ29" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CK29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CL29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CM29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CN29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CO29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CP29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CQ29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="CR29" t="inlineStr"/>
+      <c r="CS29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CT29" t="inlineStr"/>
+      <c r="CU29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CW29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CX29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CY29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CZ29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DA29" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="DB29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DC29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DD29" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="DE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG29" t="n">
         <v>2.5</v>
       </c>
-      <c r="CG29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="CH29" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CI29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CJ29" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CK29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CL29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="CM29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="CN29" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CO29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CP29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CQ29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="CR29" t="inlineStr"/>
-      <c r="CS29" t="inlineStr"/>
-      <c r="CT29" t="inlineStr"/>
-      <c r="CU29" t="inlineStr"/>
-      <c r="CV29" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="CW29" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CX29" t="inlineStr"/>
-      <c r="CY29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CZ29" t="inlineStr"/>
-      <c r="DA29" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="DB29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="DC29" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="DD29" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="DE29" t="inlineStr"/>
-      <c r="DF29" t="inlineStr"/>
-      <c r="DG29" t="inlineStr"/>
-      <c r="DH29" t="inlineStr"/>
-      <c r="DI29" t="inlineStr"/>
-      <c r="DJ29" t="inlineStr"/>
-      <c r="DK29" t="inlineStr"/>
-      <c r="DL29" t="inlineStr"/>
-      <c r="DM29" t="inlineStr"/>
-      <c r="DN29" t="inlineStr"/>
-      <c r="DO29" t="inlineStr"/>
-      <c r="DP29" t="inlineStr"/>
-      <c r="DQ29" t="inlineStr"/>
-      <c r="DR29" t="inlineStr"/>
-      <c r="DS29" t="inlineStr"/>
-      <c r="DT29" t="inlineStr"/>
-      <c r="DU29" t="inlineStr"/>
-      <c r="DV29" t="inlineStr"/>
-      <c r="DW29" t="inlineStr"/>
-      <c r="DX29" t="inlineStr"/>
-      <c r="DY29" t="inlineStr"/>
-      <c r="DZ29" t="inlineStr"/>
-      <c r="EA29" t="inlineStr"/>
-      <c r="EB29" t="inlineStr"/>
-      <c r="EC29" t="inlineStr"/>
+      <c r="DH29" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="DI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DK29" t="n">
+        <v>4</v>
+      </c>
+      <c r="DL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM29" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="DN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DP29" t="n">
+        <v>7</v>
+      </c>
+      <c r="DQ29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="DR29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV29" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="DW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX29" t="n">
+        <v>14</v>
+      </c>
+      <c r="DY29" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DZ29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="EA29" t="n">
+        <v>12</v>
+      </c>
+      <c r="EB29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="EC29" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10803,10 +11135,10 @@
         <v>12.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT30" t="n">
         <v>3</v>
@@ -10833,16 +11165,16 @@
         <v>8.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>18</v>
+        <v>21.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BF30" t="n">
         <v>1</v>
@@ -11071,10 +11403,10 @@
         <v>11</v>
       </c>
       <c r="Q31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="R31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -11098,19 +11430,19 @@
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="AB31" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AE31" t="n">
         <v>1.5</v>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
@@ -7098,41 +7098,95 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>114</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>46</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
       <c r="AF19" t="n">
         <v>0</v>
       </c>
@@ -7215,37 +7269,37 @@
         <v>2.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="BH19" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="BP19" t="n">
         <v>3</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
@@ -7254,27 +7308,31 @@
         <v>100</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>100</v>
-      </c>
-      <c r="BY19" t="inlineStr"/>
-      <c r="BZ19" t="inlineStr"/>
+        <v>66.67</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>1.7</v>
+      </c>
       <c r="CA19" t="n">
-        <v>3.78</v>
+        <v>3.96</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="CC19" t="n">
         <v>3.5</v>
@@ -7283,43 +7341,43 @@
         <v>3.28</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CK19" t="n">
         <v>1.45</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
@@ -7334,57 +7392,107 @@
         <v>1.51</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="DE19" t="inlineStr"/>
-      <c r="DF19" t="inlineStr"/>
-      <c r="DG19" t="inlineStr"/>
-      <c r="DH19" t="inlineStr"/>
-      <c r="DI19" t="inlineStr"/>
-      <c r="DJ19" t="inlineStr"/>
-      <c r="DK19" t="inlineStr"/>
-      <c r="DL19" t="inlineStr"/>
-      <c r="DM19" t="inlineStr"/>
-      <c r="DN19" t="inlineStr"/>
-      <c r="DO19" t="inlineStr"/>
-      <c r="DP19" t="inlineStr"/>
-      <c r="DQ19" t="inlineStr"/>
-      <c r="DR19" t="inlineStr"/>
-      <c r="DS19" t="inlineStr"/>
-      <c r="DT19" t="inlineStr"/>
-      <c r="DU19" t="inlineStr"/>
-      <c r="DV19" t="inlineStr"/>
-      <c r="DW19" t="inlineStr"/>
-      <c r="DX19" t="inlineStr"/>
-      <c r="DY19" t="inlineStr"/>
-      <c r="DZ19" t="inlineStr"/>
-      <c r="EA19" t="inlineStr"/>
-      <c r="EB19" t="inlineStr"/>
-      <c r="EC19" t="inlineStr"/>
+        <v>2.98</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>107</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>57</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DT19" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV19" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="DW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX19" t="n">
+        <v>12</v>
+      </c>
+      <c r="DY19" t="n">
+        <v>7</v>
+      </c>
+      <c r="DZ19" t="n">
+        <v>5</v>
+      </c>
+      <c r="EA19" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="EB19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="EC19" t="n">
+        <v>1.67</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7796,13 +7904,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -7885,65 +7993,119 @@
       <c r="AE21" t="n">
         <v>2.5</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="inlineStr"/>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr"/>
-      <c r="BA21" t="inlineStr"/>
-      <c r="BB21" t="inlineStr"/>
-      <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="inlineStr"/>
-      <c r="BE21" t="inlineStr"/>
-      <c r="BF21" t="inlineStr"/>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>41</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1</v>
+      </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="BH21" t="n">
-        <v>12</v>
+        <v>10.33</v>
       </c>
       <c r="BI21" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="BK21" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BM21" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="BN21" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BO21" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BP21" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
@@ -7955,16 +8117,16 @@
         <v>100</v>
       </c>
       <c r="BU21" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="BV21" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="BW21" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BX21" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="BY21" t="n">
         <v>2.57</v>
@@ -7973,51 +8135,55 @@
         <v>2.99</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.88</v>
+        <v>4.03</v>
       </c>
       <c r="CB21" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="CC21" t="inlineStr"/>
-      <c r="CD21" t="inlineStr"/>
+        <v>4.15</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>5</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>4.74</v>
+      </c>
       <c r="CE21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="CG21" t="n">
-        <v>3.49</v>
+        <v>3.44</v>
       </c>
       <c r="CH21" t="n">
         <v>1.6</v>
       </c>
       <c r="CI21" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="CQ21" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="CR21" t="n">
         <v>1.35</v>
@@ -8032,57 +8198,107 @@
         <v>1.72</v>
       </c>
       <c r="CV21" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="DE21" t="inlineStr"/>
-      <c r="DF21" t="inlineStr"/>
-      <c r="DG21" t="inlineStr"/>
-      <c r="DH21" t="inlineStr"/>
-      <c r="DI21" t="inlineStr"/>
-      <c r="DJ21" t="inlineStr"/>
-      <c r="DK21" t="inlineStr"/>
-      <c r="DL21" t="inlineStr"/>
-      <c r="DM21" t="inlineStr"/>
-      <c r="DN21" t="inlineStr"/>
-      <c r="DO21" t="inlineStr"/>
-      <c r="DP21" t="inlineStr"/>
-      <c r="DQ21" t="inlineStr"/>
-      <c r="DR21" t="inlineStr"/>
-      <c r="DS21" t="inlineStr"/>
-      <c r="DT21" t="inlineStr"/>
-      <c r="DU21" t="inlineStr"/>
-      <c r="DV21" t="inlineStr"/>
-      <c r="DW21" t="inlineStr"/>
-      <c r="DX21" t="inlineStr"/>
-      <c r="DY21" t="inlineStr"/>
-      <c r="DZ21" t="inlineStr"/>
-      <c r="EA21" t="inlineStr"/>
-      <c r="EB21" t="inlineStr"/>
-      <c r="EC21" t="inlineStr"/>
+        <v>2.36</v>
+      </c>
+      <c r="DE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG21" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DH21" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="DI21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DJ21" t="n">
+        <v>3</v>
+      </c>
+      <c r="DK21" t="n">
+        <v>3</v>
+      </c>
+      <c r="DL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM21" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="DN21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DO21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DP21" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="DQ21" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="DR21" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="DS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV21" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="DW21" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DX21" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="DY21" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="DZ21" t="n">
+        <v>4</v>
+      </c>
+      <c r="EA21" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="EB21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="EC21" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
@@ -1451,10 +1451,10 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB2" t="n">
         <v>4.5</v>
@@ -1463,7 +1463,7 @@
         <v>21.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="n">
         <v>3</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="DZ2" t="n">
         <v>3.25</v>
@@ -1769,7 +1769,7 @@
         <v>21</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC2" t="n">
         <v>2.75</v>
@@ -2622,7 +2622,7 @@
         <v>2.5</v>
       </c>
       <c r="P5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="n">
         <v>11</v>
@@ -2646,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55</v>
+        <v>55.5</v>
       </c>
       <c r="Y5" t="n">
         <v>0.5</v>
@@ -2934,7 +2934,7 @@
         <v>2.25</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.25</v>
+        <v>13.5</v>
       </c>
       <c r="DQ5" t="n">
         <v>11</v>
@@ -2952,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54</v>
+        <v>54.25</v>
       </c>
       <c r="DW5" t="n">
         <v>0.25</v>
@@ -3109,7 +3109,7 @@
         <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
         <v>4.5</v>
@@ -3145,7 +3145,7 @@
         <v>2.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BE6" t="n">
         <v>0.86</v>
@@ -3332,7 +3332,7 @@
         <v>14.75</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="DR6" t="n">
         <v>6.25</v>
@@ -3362,7 +3362,7 @@
         <v>5</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.25</v>
+        <v>16</v>
       </c>
       <c r="EB6" t="n">
         <v>1.4</v>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>40</v>
+        <v>39.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>41.25</v>
+        <v>41</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.5</v>
@@ -4342,7 +4342,7 @@
         <v>6.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BE9" t="n">
         <v>1.7</v>
@@ -4548,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.5</v>
+        <v>52.75</v>
       </c>
       <c r="DW9" t="n">
         <v>0.25</v>
@@ -4563,7 +4563,7 @@
         <v>4.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.75</v>
+        <v>18</v>
       </c>
       <c r="EB9" t="n">
         <v>1.45</v>
@@ -6497,7 +6497,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15.33</v>
+        <v>15.67</v>
       </c>
       <c r="AR15" t="n">
         <v>14</v>
@@ -6728,7 +6728,7 @@
         <v>2.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="DQ15" t="n">
         <v>12</v>
@@ -6846,7 +6846,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="AR16" t="n">
         <v>10.75</v>
@@ -6879,16 +6879,16 @@
         <v>9.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BD16" t="n">
         <v>15.25</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="BF16" t="n">
         <v>0.75</v>
@@ -7513,7 +7513,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q18" t="n">
         <v>14</v>
@@ -7537,25 +7537,25 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
         <v>8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -7821,7 +7821,7 @@
         <v>1</v>
       </c>
       <c r="DP18" t="n">
-        <v>15</v>
+        <v>14.67</v>
       </c>
       <c r="DQ18" t="n">
         <v>14.67</v>
@@ -7839,25 +7839,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>45.33</v>
+        <v>45</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="DY18" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="EA18" t="n">
         <v>12.33</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="EC18" t="n">
         <v>2.67</v>
@@ -8721,7 +8721,7 @@
         <v>11.67</v>
       </c>
       <c r="Q21" t="n">
-        <v>14.67</v>
+        <v>14.33</v>
       </c>
       <c r="R21" t="n">
         <v>8.67</v>
@@ -9033,7 +9033,7 @@
         <v>10.5</v>
       </c>
       <c r="DQ21" t="n">
-        <v>15.25</v>
+        <v>15</v>
       </c>
       <c r="DR21" t="n">
         <v>9.25</v>
@@ -12732,7 +12732,7 @@
         <v>2.33</v>
       </c>
       <c r="P31" t="n">
-        <v>14.67</v>
+        <v>15</v>
       </c>
       <c r="Q31" t="n">
         <v>16.33</v>
@@ -13040,7 +13040,7 @@
         <v>2.5</v>
       </c>
       <c r="DP31" t="n">
-        <v>13.25</v>
+        <v>13.5</v>
       </c>
       <c r="DQ31" t="n">
         <v>14.75</v>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
@@ -6497,7 +6497,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15.67</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
         <v>14</v>
@@ -6728,7 +6728,7 @@
         <v>2.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="DQ15" t="n">
         <v>12</v>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
@@ -2707,7 +2707,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15</v>
+        <v>14.33</v>
       </c>
       <c r="AR5" t="n">
         <v>11</v>
@@ -2938,7 +2938,7 @@
         <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="DQ5" t="n">
         <v>11</v>
@@ -4226,7 +4226,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>14</v>
+        <v>14.67</v>
       </c>
       <c r="Q9" t="n">
         <v>13.33</v>
@@ -4250,7 +4250,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>52.67</v>
+        <v>52.33</v>
       </c>
       <c r="Y9" t="n">
         <v>0.33</v>
@@ -4534,7 +4534,7 @@
         <v>2.2</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="DQ9" t="n">
         <v>12.8</v>
@@ -4552,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
       <c r="DW9" t="n">
         <v>0.4</v>
@@ -5458,7 +5458,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
@@ -5803,7 +5803,7 @@
         <v>3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR13" t="n">
         <v>10.5</v>
@@ -6034,7 +6034,7 @@
         <v>2.2</v>
       </c>
       <c r="DP13" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DQ13" t="n">
         <v>12.6</v>
@@ -6528,7 +6528,7 @@
         <v>1.5</v>
       </c>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q15" t="n">
         <v>9.5</v>
@@ -6840,7 +6840,7 @@
         <v>2.2</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="DQ15" t="n">
         <v>12.2</v>
@@ -6958,7 +6958,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="AR16" t="n">
         <v>12.4</v>
@@ -6982,7 +6982,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.2</v>
@@ -9237,7 +9237,7 @@
         <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>14</v>
+        <v>13.67</v>
       </c>
       <c r="Q22" t="n">
         <v>14.67</v>
@@ -9549,7 +9549,7 @@
         <v>2.2</v>
       </c>
       <c r="DP22" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="DQ22" t="n">
         <v>15.4</v>
@@ -10120,7 +10120,7 @@
         <v>3</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6.33</v>
+        <v>9.33</v>
       </c>
       <c r="AR24" t="n">
         <v>14</v>
@@ -10144,7 +10144,7 @@
         <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>40.33</v>
+        <v>40</v>
       </c>
       <c r="AZ24" t="n">
         <v>0</v>
@@ -10351,7 +10351,7 @@
         <v>3</v>
       </c>
       <c r="DP24" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DQ24" t="n">
         <v>11.8</v>
@@ -10369,7 +10369,7 @@
         <v>0</v>
       </c>
       <c r="DV24" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="DW24" t="n">
         <v>0</v>
@@ -10845,7 +10845,7 @@
         <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>7.67</v>
+        <v>11</v>
       </c>
       <c r="Q26" t="n">
         <v>12.33</v>
@@ -10869,25 +10869,25 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>64</v>
+        <v>64.33</v>
       </c>
       <c r="Y26" t="n">
         <v>0.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>11.33</v>
+        <v>11.67</v>
       </c>
       <c r="AA26" t="n">
         <v>5.33</v>
       </c>
       <c r="AB26" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="AC26" t="n">
         <v>17.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -11153,7 +11153,7 @@
         <v>2.6</v>
       </c>
       <c r="DP26" t="n">
-        <v>8.800000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="DQ26" t="n">
         <v>12.4</v>
@@ -11171,25 +11171,25 @@
         <v>0</v>
       </c>
       <c r="DV26" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
       <c r="DW26" t="n">
         <v>0.2</v>
       </c>
       <c r="DX26" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="DY26" t="n">
         <v>5.4</v>
       </c>
       <c r="DZ26" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="EA26" t="n">
         <v>18.4</v>
       </c>
       <c r="EB26" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="EC26" t="n">
         <v>1.8</v>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
@@ -4226,7 +4226,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>14.67</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
         <v>13.33</v>
@@ -4534,7 +4534,7 @@
         <v>2.2</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="DQ9" t="n">
         <v>12.8</v>
@@ -5458,7 +5458,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
@@ -6958,7 +6958,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="AR16" t="n">
         <v>12.4</v>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
@@ -2707,7 +2707,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.33</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
         <v>11</v>
@@ -2938,7 +2938,7 @@
         <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="DQ5" t="n">
         <v>11</v>
@@ -3793,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
         <v>3.5</v>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K8" t="n">
         <v>4.5</v>
@@ -3823,7 +3823,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Q8" t="n">
         <v>12</v>
@@ -3868,7 +3868,7 @@
         <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -4105,7 +4105,7 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DG8" t="n">
         <v>2.8</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="DK8" t="n">
         <v>4.4</v>
@@ -4135,7 +4135,7 @@
         <v>1.6</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="DQ8" t="n">
         <v>11.2</v>
@@ -4174,7 +4174,7 @@
         <v>1.02</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="9">
@@ -4598,7 +4598,7 @@
         <v>1.25</v>
       </c>
       <c r="G10" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="H10" t="n">
         <v>76.75</v>
@@ -4613,7 +4613,7 @@
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>35.5</v>
@@ -4622,7 +4622,7 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
         <v>13.25</v>
@@ -4781,10 +4781,10 @@
         <v>2.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BR10" t="n">
         <v>80</v>
@@ -4910,7 +4910,7 @@
         <v>1.2</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="DH10" t="n">
         <v>77.40000000000001</v>
@@ -4925,7 +4925,7 @@
         <v>4.6</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="DM10" t="n">
         <v>37.8</v>
@@ -4934,7 +4934,7 @@
         <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="DP10" t="n">
         <v>13.4</v>
@@ -5034,7 +5034,7 @@
         <v>14.33</v>
       </c>
       <c r="R11" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="S11" t="n">
         <v>1.67</v>
@@ -5346,7 +5346,7 @@
         <v>14.75</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5428,7 +5428,7 @@
         <v>0.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
         <v>2.4</v>
@@ -5440,7 +5440,7 @@
         <v>0.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL12" t="n">
         <v>4.8</v>
@@ -5503,7 +5503,7 @@
         <v>1.44</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="BG12" t="n">
         <v>3.4</v>
@@ -6609,7 +6609,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16</v>
+        <v>15.67</v>
       </c>
       <c r="AR15" t="n">
         <v>14</v>
@@ -6840,7 +6840,7 @@
         <v>2.2</v>
       </c>
       <c r="DP15" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="DQ15" t="n">
         <v>12.2</v>
@@ -6958,7 +6958,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="AR16" t="n">
         <v>12.4</v>
@@ -7276,7 +7276,7 @@
         <v>2.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>77.5</v>
@@ -7291,7 +7291,7 @@
         <v>3</v>
       </c>
       <c r="AM17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
         <v>24.5</v>
@@ -7300,7 +7300,7 @@
         <v>1.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>10.5</v>
@@ -7378,10 +7378,10 @@
         <v>1.6</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="BR17" t="n">
         <v>80</v>
@@ -7507,7 +7507,7 @@
         <v>1.4</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="DH17" t="n">
         <v>90</v>
@@ -7522,7 +7522,7 @@
         <v>3.8</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="DM17" t="n">
         <v>32</v>
@@ -7531,7 +7531,7 @@
         <v>0.6</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="DP17" t="n">
         <v>12.6</v>
@@ -8028,7 +8028,7 @@
         <v>2.33</v>
       </c>
       <c r="P19" t="n">
-        <v>13.67</v>
+        <v>14</v>
       </c>
       <c r="Q19" t="n">
         <v>15</v>
@@ -8340,7 +8340,7 @@
         <v>1.8</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="DQ19" t="n">
         <v>14.2</v>
@@ -9237,7 +9237,7 @@
         <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>13.67</v>
+        <v>14</v>
       </c>
       <c r="Q22" t="n">
         <v>14.67</v>
@@ -9288,7 +9288,7 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AH22" t="n">
         <v>4.5</v>
@@ -9300,7 +9300,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AL22" t="n">
         <v>5.5</v>
@@ -9318,7 +9318,7 @@
         <v>1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR22" t="n">
         <v>16.5</v>
@@ -9363,7 +9363,7 @@
         <v>1.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="BG22" t="n">
         <v>2.4</v>
@@ -9519,7 +9519,7 @@
         <v>0</v>
       </c>
       <c r="DF22" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG22" t="n">
         <v>4.4</v>
@@ -9531,7 +9531,7 @@
         <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="DK22" t="n">
         <v>6.6</v>
@@ -9549,7 +9549,7 @@
         <v>2.2</v>
       </c>
       <c r="DP22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DQ22" t="n">
         <v>15.4</v>
@@ -9588,7 +9588,7 @@
         <v>1.56</v>
       </c>
       <c r="EC22" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
@@ -2230,7 +2230,7 @@
         <v>9.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="R4" t="n">
         <v>8.5</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>56.25</v>
+        <v>55</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>7.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>12</v>
+        <v>16.25</v>
       </c>
       <c r="AD4" t="n">
         <v>1.71</v>
@@ -2542,7 +2542,7 @@
         <v>8.33</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.17</v>
+        <v>13.17</v>
       </c>
       <c r="DR4" t="n">
         <v>7.5</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>51.67</v>
+        <v>50.83</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
@@ -2572,7 +2572,7 @@
         <v>5.83</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.17</v>
+        <v>19</v>
       </c>
       <c r="EB4" t="n">
         <v>1.42</v>
@@ -3153,7 +3153,7 @@
         <v>4.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>16.5</v>
+        <v>16.75</v>
       </c>
       <c r="BE6" t="n">
         <v>1.14</v>
@@ -3374,7 +3374,7 @@
         <v>5.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.17</v>
+        <v>16.33</v>
       </c>
       <c r="EB6" t="n">
         <v>1.41</v>
@@ -3483,7 +3483,7 @@
         <v>0.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AH7" t="n">
         <v>3.25</v>
@@ -3495,7 +3495,7 @@
         <v>0.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>6.75</v>
@@ -3558,7 +3558,7 @@
         <v>1.53</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="BG7" t="n">
         <v>2.83</v>
@@ -3710,7 +3710,7 @@
         <v>0.33</v>
       </c>
       <c r="DF7" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DG7" t="n">
         <v>2</v>
@@ -3722,7 +3722,7 @@
         <v>0.17</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DK7" t="n">
         <v>6.67</v>
@@ -3779,7 +3779,7 @@
         <v>1.43</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -4315,7 +4315,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.33</v>
+        <v>10.67</v>
       </c>
       <c r="AR9" t="n">
         <v>12</v>
@@ -4542,7 +4542,7 @@
         <v>2.34</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.16</v>
+        <v>12.34</v>
       </c>
       <c r="DQ9" t="n">
         <v>12.66</v>
@@ -5039,7 +5039,7 @@
         <v>8.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>14.25</v>
+        <v>14</v>
       </c>
       <c r="R11" t="n">
         <v>6.75</v>
@@ -5351,7 +5351,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="DQ11" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="DR11" t="n">
         <v>6.4</v>
@@ -5469,10 +5469,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB12" t="n">
         <v>8</v>
@@ -5481,7 +5481,7 @@
         <v>13</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.5</v>
+        <v>15.67</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.83</v>
+        <v>10</v>
       </c>
       <c r="DZ12" t="n">
         <v>5.67</v>
@@ -5783,7 +5783,7 @@
         <v>17.67</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="EC12" t="n">
         <v>2.17</v>
@@ -7453,10 +7453,10 @@
         <v>0.33</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="BB17" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="BC17" t="n">
         <v>3</v>
@@ -7465,7 +7465,7 @@
         <v>20.67</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="BF17" t="n">
         <v>2.67</v>
@@ -7678,10 +7678,10 @@
         <v>0.16</v>
       </c>
       <c r="DX17" t="n">
-        <v>12</v>
+        <v>12.16</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.84</v>
+        <v>7</v>
       </c>
       <c r="DZ17" t="n">
         <v>5.16</v>
@@ -7690,7 +7690,7 @@
         <v>20.5</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC17" t="n">
         <v>1.67</v>
@@ -8121,7 +8121,7 @@
         <v>0.5</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
         <v>80.25</v>
@@ -8136,7 +8136,7 @@
         <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="M19" t="n">
         <v>31.25</v>
@@ -8145,13 +8145,13 @@
         <v>0.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
         <v>12.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.5</v>
+        <v>14.25</v>
       </c>
       <c r="R19" t="n">
         <v>5.5</v>
@@ -8172,25 +8172,25 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>53</v>
+        <v>54.25</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="AB19" t="n">
         <v>6.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>12</v>
+        <v>15.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -8304,10 +8304,10 @@
         <v>1.67</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.33</v>
+        <v>3.83</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
@@ -8433,7 +8433,7 @@
         <v>0.67</v>
       </c>
       <c r="DG19" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DH19" t="n">
         <v>88</v>
@@ -8448,7 +8448,7 @@
         <v>4</v>
       </c>
       <c r="DL19" t="n">
-        <v>-0.17</v>
+        <v>0.17</v>
       </c>
       <c r="DM19" t="n">
         <v>41.67</v>
@@ -8457,13 +8457,13 @@
         <v>0.83</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="DP19" t="n">
         <v>13.17</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12</v>
+        <v>13.83</v>
       </c>
       <c r="DR19" t="n">
         <v>6.5</v>
@@ -8478,25 +8478,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.67</v>
+        <v>55.5</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.67</v>
+        <v>12.5</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.83</v>
+        <v>6.67</v>
       </c>
       <c r="DZ19" t="n">
         <v>5.83</v>
       </c>
       <c r="EA19" t="n">
-        <v>12.67</v>
+        <v>14.83</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC19" t="n">
         <v>1.5</v>
@@ -8554,7 +8554,7 @@
         <v>11.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="R20" t="n">
         <v>6</v>
@@ -8866,7 +8866,7 @@
         <v>10.83</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.66</v>
+        <v>10.83</v>
       </c>
       <c r="DR20" t="n">
         <v>6.66</v>
@@ -9441,7 +9441,7 @@
         <v>16.67</v>
       </c>
       <c r="AR22" t="n">
-        <v>11.33</v>
+        <v>14.33</v>
       </c>
       <c r="AS22" t="n">
         <v>4</v>
@@ -9462,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>48.67</v>
+        <v>50.33</v>
       </c>
       <c r="AZ22" t="n">
         <v>0.33</v>
@@ -9477,7 +9477,7 @@
         <v>3</v>
       </c>
       <c r="BD22" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BE22" t="n">
         <v>1.57</v>
@@ -9672,7 +9672,7 @@
         <v>15.34</v>
       </c>
       <c r="DQ22" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="DR22" t="n">
         <v>4.34</v>
@@ -9687,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>48.5</v>
+        <v>49.33</v>
       </c>
       <c r="DW22" t="n">
         <v>0.33</v>
@@ -9702,7 +9702,7 @@
         <v>3.33</v>
       </c>
       <c r="EA22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="EB22" t="n">
         <v>1.59</v>
@@ -11445,7 +11445,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR27" t="n">
         <v>8.4</v>
@@ -11676,7 +11676,7 @@
         <v>1.83</v>
       </c>
       <c r="DP27" t="n">
-        <v>9.67</v>
+        <v>9.5</v>
       </c>
       <c r="DQ27" t="n">
         <v>9.83</v>
@@ -12220,7 +12220,7 @@
         <v>0.67</v>
       </c>
       <c r="AH29" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AI29" t="n">
         <v>85.33</v>
@@ -12235,7 +12235,7 @@
         <v>5</v>
       </c>
       <c r="AM29" t="n">
-        <v>-0.33</v>
+        <v>0.33</v>
       </c>
       <c r="AN29" t="n">
         <v>43.33</v>
@@ -12244,16 +12244,16 @@
         <v>0.67</v>
       </c>
       <c r="AP29" t="n">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AQ29" t="n">
         <v>11</v>
       </c>
       <c r="AR29" t="n">
-        <v>8</v>
+        <v>10.33</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="AT29" t="n">
         <v>1.67</v>
@@ -12271,7 +12271,7 @@
         <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>45.67</v>
+        <v>44</v>
       </c>
       <c r="AZ29" t="n">
         <v>0</v>
@@ -12286,7 +12286,7 @@
         <v>3</v>
       </c>
       <c r="BD29" t="n">
-        <v>9</v>
+        <v>16.33</v>
       </c>
       <c r="BE29" t="n">
         <v>1.32</v>
@@ -12322,10 +12322,10 @@
         <v>0.67</v>
       </c>
       <c r="BP29" t="n">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="BQ29" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BR29" t="n">
         <v>100</v>
@@ -12451,7 +12451,7 @@
         <v>0.84</v>
       </c>
       <c r="DG29" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="DH29" t="n">
         <v>99.83</v>
@@ -12466,7 +12466,7 @@
         <v>5.84</v>
       </c>
       <c r="DL29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="DM29" t="n">
         <v>54.66</v>
@@ -12475,16 +12475,16 @@
         <v>0.84</v>
       </c>
       <c r="DO29" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="DP29" t="n">
         <v>9.67</v>
       </c>
       <c r="DQ29" t="n">
-        <v>8.67</v>
+        <v>9.83</v>
       </c>
       <c r="DR29" t="n">
-        <v>5.33</v>
+        <v>5.16</v>
       </c>
       <c r="DS29" t="n">
         <v>0</v>
@@ -12496,7 +12496,7 @@
         <v>0</v>
       </c>
       <c r="DV29" t="n">
-        <v>49.84</v>
+        <v>49</v>
       </c>
       <c r="DW29" t="n">
         <v>0</v>
@@ -12511,7 +12511,7 @@
         <v>5.16</v>
       </c>
       <c r="EA29" t="n">
-        <v>13.66</v>
+        <v>17.33</v>
       </c>
       <c r="EB29" t="n">
         <v>1.63</v>
@@ -12608,7 +12608,7 @@
         <v>6</v>
       </c>
       <c r="AC30" t="n">
-        <v>18.67</v>
+        <v>18.33</v>
       </c>
       <c r="AD30" t="n">
         <v>1.59</v>
@@ -12914,7 +12914,7 @@
         <v>5</v>
       </c>
       <c r="EA30" t="n">
-        <v>19.5</v>
+        <v>19.33</v>
       </c>
       <c r="EB30" t="n">
         <v>1.36</v>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
@@ -6265,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>45.25</v>
+        <v>45.5</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.33</v>
+        <v>48.5</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
@@ -9059,7 +9059,7 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>42.67</v>
+        <v>42.33</v>
       </c>
       <c r="AZ21" t="n">
         <v>0.33</v>
@@ -9284,7 +9284,7 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>41.67</v>
+        <v>41.5</v>
       </c>
       <c r="DW21" t="n">
         <v>0.33</v>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2026.xlsx
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>40.88</v>
+        <v>40.75</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.12</v>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47.2</v>
+        <v>47.13</v>
       </c>
       <c r="DW3" t="n">
         <v>0.06</v>
@@ -2218,7 +2218,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.44</v>
+        <v>13.22</v>
       </c>
       <c r="R4" t="n">
         <v>7.44</v>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.33</v>
+        <v>49.89</v>
       </c>
       <c r="Y4" t="n">
         <v>0.11</v>
@@ -2530,7 +2530,7 @@
         <v>9.34</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.86</v>
+        <v>12.13</v>
       </c>
       <c r="DR4" t="n">
         <v>7.93</v>
@@ -2545,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.07</v>
+        <v>47.4</v>
       </c>
       <c r="DW4" t="n">
         <v>0.07000000000000001</v>
@@ -5160,7 +5160,7 @@
         <v>3</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.5</v>
+        <v>9.57</v>
       </c>
       <c r="BI11" t="n">
         <v>3</v>
@@ -5815,7 +5815,7 @@
         <v>2.57</v>
       </c>
       <c r="K13" t="n">
-        <v>5.71</v>
+        <v>5.86</v>
       </c>
       <c r="L13" t="n">
         <v>-0.14</v>
@@ -5962,7 +5962,7 @@
         <v>2.93</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.27</v>
+        <v>8.33</v>
       </c>
       <c r="BI13" t="n">
         <v>2.93</v>
@@ -6127,7 +6127,7 @@
         <v>2.27</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.13</v>
+        <v>5.2</v>
       </c>
       <c r="DL13" t="n">
         <v>-0.13</v>
@@ -7929,7 +7929,7 @@
         <v>11.83</v>
       </c>
       <c r="AR18" t="n">
-        <v>13</v>
+        <v>11.83</v>
       </c>
       <c r="AS18" t="n">
         <v>7.83</v>
@@ -7950,7 +7950,7 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>46.17</v>
+        <v>45.33</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -8160,7 +8160,7 @@
         <v>11.14</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.64</v>
+        <v>13.14</v>
       </c>
       <c r="DR18" t="n">
         <v>7.14</v>
@@ -8175,7 +8175,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.86</v>
+        <v>48.5</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>50.67</v>
+        <v>50.83</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -12596,7 +12596,7 @@
         <v>0</v>
       </c>
       <c r="DV29" t="n">
-        <v>49.29</v>
+        <v>49.36</v>
       </c>
       <c r="DW29" t="n">
         <v>0.14</v>
